--- a/athens_events.xlsx
+++ b/athens_events.xlsx
@@ -185,6 +185,24 @@
     <t>Ciné</t>
   </si>
   <si>
+    <t>Great Southland Stampede Rodeo</t>
+  </si>
+  <si>
+    <t>Sports</t>
+  </si>
+  <si>
+    <t>UGA Livestock Instructional Arena</t>
+  </si>
+  <si>
+    <t>UGA Baseball V Kentucky</t>
+  </si>
+  <si>
+    <t>Foley Field</t>
+  </si>
+  <si>
+    <t>UGA Baseball v. Kentucky</t>
+  </si>
+  <si>
     <t>Sips n Thrifts</t>
   </si>
   <si>
@@ -200,9 +218,6 @@
     <t>Classic City Pétanque Club</t>
   </si>
   <si>
-    <t>Sports</t>
-  </si>
-  <si>
     <t>Lay Park</t>
   </si>
   <si>
@@ -539,6 +554,12 @@
     <t>Dr. Fred's Karaoke</t>
   </si>
   <si>
+    <t>UGA Softball V GA State</t>
+  </si>
+  <si>
+    <t>Jack Turner Stadium</t>
+  </si>
+  <si>
     <t>Jazz Jam</t>
   </si>
   <si>
@@ -620,6 +641,12 @@
     <t>Attest, Frisson, Greylow</t>
   </si>
   <si>
+    <t>UGA Softball vs. LSU</t>
+  </si>
+  <si>
+    <t>Turner Softball Stadium</t>
+  </si>
+  <si>
     <t>Historic Athens Heritage Walk</t>
   </si>
   <si>
@@ -659,36 +686,75 @@
     <t>Tween STEAM Club</t>
   </si>
   <si>
+    <t>UGA Baseball v. West Georgia</t>
+  </si>
+  <si>
     <t>Local 707</t>
   </si>
   <si>
     <t>Penny Loafer Debut EP Release Show</t>
   </si>
   <si>
+    <t>UGA Softball vs. Oklahoma State</t>
+  </si>
+  <si>
     <t>Emo Nite</t>
   </si>
   <si>
+    <t>SEC Equestrian Championship</t>
+  </si>
+  <si>
+    <t>UGA Equestrian Complex</t>
+  </si>
+  <si>
+    <t>UGA Baseball v. Auburn</t>
+  </si>
+  <si>
+    <t>UGA Baseball v. Queens University of Charlotte</t>
+  </si>
+  <si>
     <t>Palmyra</t>
   </si>
   <si>
     <t>Local 708</t>
   </si>
   <si>
+    <t>UGA Softball vs. Mercer</t>
+  </si>
+  <si>
     <t>Pasadena</t>
   </si>
   <si>
     <t>49 Winchester</t>
   </si>
   <si>
+    <t>UGA Softball vs. Texas A&amp;M</t>
+  </si>
+  <si>
     <t>Roomate</t>
   </si>
   <si>
+    <t>UGA Baseball v. Presbyterian</t>
+  </si>
+  <si>
     <t>Local 709</t>
   </si>
   <si>
+    <t>UGA Softball vs. USC-Upstate</t>
+  </si>
+  <si>
     <t>Nightly</t>
   </si>
   <si>
+    <t>UGA Baseball v. Arkansas</t>
+  </si>
+  <si>
+    <t>G-Day!</t>
+  </si>
+  <si>
+    <t>Sanford Stadium</t>
+  </si>
+  <si>
     <t>Flipturn</t>
   </si>
   <si>
@@ -701,6 +767,9 @@
     <t>United We Dance: The Ultimate Rave Experience</t>
   </si>
   <si>
+    <t>UGA Softball vs. Ole Miss</t>
+  </si>
+  <si>
     <t>Abbery Road Live!</t>
   </si>
   <si>
@@ -710,12 +779,18 @@
     <t>Evan Honer</t>
   </si>
   <si>
+    <t>UGA Baseball v. Oklahoma</t>
+  </si>
+  <si>
     <t>Daniel Donato's Cosmis Country</t>
   </si>
   <si>
     <t>Julien Baker &amp; Torres - Send a Prayer My Way Tour</t>
   </si>
   <si>
+    <t>UGA Baseball v. Kennesaw State</t>
+  </si>
+  <si>
     <t>Local 712</t>
   </si>
   <si>
@@ -734,85 +809,10 @@
     <t>Health</t>
   </si>
   <si>
+    <t>UGA Baseball v. Texas A&amp;M</t>
+  </si>
+  <si>
     <t>Sanguisugabogg</t>
-  </si>
-  <si>
-    <t>Great Southland Stampede Rodeo</t>
-  </si>
-  <si>
-    <t>UGA Livestock Instructional Arena</t>
-  </si>
-  <si>
-    <t>UGA Baseball V Kentucky</t>
-  </si>
-  <si>
-    <t>Foley Field</t>
-  </si>
-  <si>
-    <t>UGA Softball V GA State</t>
-  </si>
-  <si>
-    <t>Jack Turner Stadium</t>
-  </si>
-  <si>
-    <t>SEC Equestrian Championship</t>
-  </si>
-  <si>
-    <t>UGA Equestrian Complex</t>
-  </si>
-  <si>
-    <t>G-Day!</t>
-  </si>
-  <si>
-    <t>Sanford Stadium</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Kentucky</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. West Georgia</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Auburn</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Queens University of Charlotte</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Presbyterian</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Arkansas</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Oklahoma</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Kennesaw State</t>
-  </si>
-  <si>
-    <t>UGA Baseball v. Texas A&amp;M</t>
-  </si>
-  <si>
-    <t>UGA Softball vs. LSU</t>
-  </si>
-  <si>
-    <t>Turner Softball Stadium</t>
-  </si>
-  <si>
-    <t>UGA Softball vs. Oklahoma State</t>
-  </si>
-  <si>
-    <t>UGA Softball vs. Mercer</t>
-  </si>
-  <si>
-    <t>UGA Softball vs. Texas A&amp;M</t>
-  </si>
-  <si>
-    <t>UGA Softball vs. USC-Upstate</t>
-  </si>
-  <si>
-    <t>UGA Softball vs. Ole Miss</t>
   </si>
   <si>
     <t>Column 3</t>
@@ -1126,11 +1126,32 @@
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1147,31 +1168,16 @@
     <xf borderId="5" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1179,12 +1185,6 @@
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -2082,80 +2082,80 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>45732.0</v>
-      </c>
-      <c r="D28" s="7">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="B28" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="8">
-        <v>0.0</v>
+      <c r="C28" s="26">
+        <v>45731.0</v>
+      </c>
+      <c r="D28" s="27">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="28">
+        <v>10.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="21">
-        <v>45732.0</v>
-      </c>
-      <c r="D29" s="22">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="A29" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="F29" s="23">
-        <v>5.0</v>
+      <c r="B29" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="31">
+        <v>45731.0</v>
+      </c>
+      <c r="D29" s="32">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="33">
+        <v>12.0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="26">
+        <v>45731.0</v>
+      </c>
+      <c r="D30" s="27">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="6">
-        <v>45732.0</v>
-      </c>
-      <c r="D30" s="7">
-        <v>0.5625</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="8">
+      <c r="F30" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C31" s="21">
         <v>45732.0</v>
       </c>
       <c r="D31" s="22">
-        <v>0.625</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F31" s="23">
         <v>0.0</v>
@@ -2166,38 +2166,38 @@
         <v>65</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C32" s="6">
         <v>45732.0</v>
       </c>
       <c r="D32" s="7">
-        <v>0.6666666666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>66</v>
       </c>
       <c r="F32" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="11">
+      <c r="B33" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="21">
         <v>45732.0</v>
       </c>
-      <c r="D33" s="12">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="22">
+        <v>0.5625</v>
+      </c>
+      <c r="E33" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="23">
         <v>0.0</v>
       </c>
     </row>
@@ -2206,16 +2206,16 @@
         <v>69</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C34" s="6">
         <v>45732.0</v>
       </c>
       <c r="D34" s="7">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F34" s="8">
         <v>0.0</v>
@@ -2223,79 +2223,79 @@
     </row>
     <row r="35">
       <c r="A35" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C35" s="21">
         <v>45732.0</v>
       </c>
       <c r="D35" s="22">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F35" s="23">
         <v>0.0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="16">
+        <v>45732.0</v>
+      </c>
+      <c r="D36" s="17">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C36" s="6">
-        <v>45732.0</v>
-      </c>
-      <c r="D36" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F36" s="8">
-        <v>20.0</v>
+      <c r="F36" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="C37" s="21">
         <v>45732.0</v>
       </c>
       <c r="D37" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F37" s="23">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C38" s="6">
         <v>45732.0</v>
       </c>
       <c r="D38" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F38" s="8">
         <v>0.0</v>
@@ -2303,59 +2303,59 @@
     </row>
     <row r="39">
       <c r="A39" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C39" s="21">
         <v>45732.0</v>
       </c>
       <c r="D39" s="22">
-        <v>0.8125</v>
+        <v>0.75</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F39" s="23">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="C40" s="6">
         <v>45732.0</v>
       </c>
       <c r="D40" s="7">
-        <v>0.8333333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F40" s="8">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C41" s="21">
         <v>45732.0</v>
       </c>
       <c r="D41" s="22">
-        <v>0.8541666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="F41" s="23">
         <v>0.0</v>
@@ -2366,56 +2366,56 @@
         <v>85</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C42" s="6">
         <v>45732.0</v>
       </c>
       <c r="D42" s="7">
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>86</v>
       </c>
       <c r="F42" s="8">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C43" s="21">
-        <v>45733.0</v>
+        <v>45732.0</v>
       </c>
       <c r="D43" s="22">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F43" s="23">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C44" s="6">
-        <v>45733.0</v>
+        <v>45732.0</v>
       </c>
       <c r="D44" s="7">
-        <v>0.4166666666666667</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F44" s="8">
         <v>0.0</v>
@@ -2426,56 +2426,56 @@
         <v>90</v>
       </c>
       <c r="B45" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="21">
+        <v>45732.0</v>
+      </c>
+      <c r="D45" s="22">
+        <v>0.875</v>
+      </c>
+      <c r="E45" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="21">
-        <v>45733.0</v>
-      </c>
-      <c r="D45" s="22">
-        <v>0.4375</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>27</v>
-      </c>
       <c r="F45" s="23">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="6">
-        <v>45733.0</v>
-      </c>
-      <c r="D46" s="7">
-        <v>0.4791666666666667</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F46" s="8">
+      <c r="A46" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="26">
+        <v>45732.0</v>
+      </c>
+      <c r="D46" s="27">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C47" s="21">
         <v>45733.0</v>
       </c>
       <c r="D47" s="22">
-        <v>0.75</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="F47" s="23">
         <v>0.0</v>
@@ -2483,39 +2483,39 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="C48" s="6">
         <v>45733.0</v>
       </c>
       <c r="D48" s="7">
-        <v>0.75</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F48" s="8">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="20" t="s">
         <v>96</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>16</v>
       </c>
       <c r="C49" s="21">
         <v>45733.0</v>
       </c>
       <c r="D49" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.4375</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F49" s="23">
         <v>0.0</v>
@@ -2526,16 +2526,16 @@
         <v>97</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="C50" s="6">
         <v>45733.0</v>
       </c>
       <c r="D50" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F50" s="8">
         <v>0.0</v>
@@ -2546,76 +2546,76 @@
         <v>99</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C51" s="21">
         <v>45733.0</v>
       </c>
       <c r="D51" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="F51" s="23">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="29">
+      <c r="A52" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="6">
         <v>45733.0</v>
       </c>
-      <c r="D52" s="30">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F52" s="31">
-        <v>0.0</v>
+      <c r="D52" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F52" s="8">
+        <v>15.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="C53" s="21">
         <v>45733.0</v>
       </c>
       <c r="D53" s="22">
-        <v>0.8125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="F53" s="23">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6">
         <v>45733.0</v>
       </c>
       <c r="D54" s="7">
-        <v>0.8333333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="F54" s="8">
         <v>0.0</v>
@@ -2623,79 +2623,79 @@
     </row>
     <row r="55">
       <c r="A55" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C55" s="21">
         <v>45733.0</v>
       </c>
       <c r="D55" s="22">
-        <v>0.8333333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F55" s="23">
         <v>10.0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="6">
+      <c r="A56" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="36">
         <v>45733.0</v>
       </c>
-      <c r="D56" s="7">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F56" s="8">
-        <v>10.0</v>
+      <c r="D56" s="37">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E56" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C57" s="21">
-        <v>45734.0</v>
+        <v>45733.0</v>
       </c>
       <c r="D57" s="22">
-        <v>0.3333333333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F57" s="23">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C58" s="6">
-        <v>45734.0</v>
+        <v>45733.0</v>
       </c>
       <c r="D58" s="7">
-        <v>0.4583333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F58" s="8">
         <v>0.0</v>
@@ -2703,22 +2703,22 @@
     </row>
     <row r="59">
       <c r="A59" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="21">
+        <v>45733.0</v>
+      </c>
+      <c r="D59" s="22">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E59" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B59" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" s="21">
-        <v>45734.0</v>
-      </c>
-      <c r="D59" s="22">
-        <v>0.4791666666666667</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>29</v>
-      </c>
       <c r="F59" s="23">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="60">
@@ -2726,36 +2726,36 @@
         <v>114</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C60" s="6">
-        <v>45734.0</v>
+        <v>45733.0</v>
       </c>
       <c r="D60" s="7">
-        <v>0.4791666666666667</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="F60" s="8">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="C61" s="21">
         <v>45734.0</v>
       </c>
       <c r="D61" s="22">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="F61" s="23">
         <v>0.0</v>
@@ -2763,19 +2763,19 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C62" s="6">
         <v>45734.0</v>
       </c>
       <c r="D62" s="7">
-        <v>0.5625</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="F62" s="8">
         <v>0.0</v>
@@ -2783,19 +2783,19 @@
     </row>
     <row r="63">
       <c r="A63" s="19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C63" s="21">
         <v>45734.0</v>
       </c>
       <c r="D63" s="22">
-        <v>0.6458333333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F63" s="23">
         <v>0.0</v>
@@ -2803,19 +2803,19 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="C64" s="6">
         <v>45734.0</v>
       </c>
       <c r="D64" s="7">
-        <v>0.6666666666666666</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="F64" s="8">
         <v>0.0</v>
@@ -2826,13 +2826,13 @@
         <v>120</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C65" s="21">
         <v>45734.0</v>
       </c>
       <c r="D65" s="22">
-        <v>0.6875</v>
+        <v>0.5</v>
       </c>
       <c r="E65" s="20" t="s">
         <v>27</v>
@@ -2843,19 +2843,19 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C66" s="6">
         <v>45734.0</v>
       </c>
       <c r="D66" s="7">
-        <v>0.7291666666666666</v>
+        <v>0.5625</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="F66" s="8">
         <v>0.0</v>
@@ -2863,19 +2863,19 @@
     </row>
     <row r="67">
       <c r="A67" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C67" s="21">
         <v>45734.0</v>
       </c>
       <c r="D67" s="22">
-        <v>0.7291666666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="F67" s="23">
         <v>0.0</v>
@@ -2883,19 +2883,19 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C68" s="6">
         <v>45734.0</v>
       </c>
       <c r="D68" s="7">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="F68" s="8">
         <v>0.0</v>
@@ -2906,16 +2906,16 @@
         <v>125</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C69" s="21">
         <v>45734.0</v>
       </c>
       <c r="D69" s="22">
-        <v>0.7708333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="F69" s="23">
         <v>0.0</v>
@@ -2923,19 +2923,19 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C70" s="6">
         <v>45734.0</v>
       </c>
       <c r="D70" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="F70" s="8">
         <v>0.0</v>
@@ -2952,10 +2952,10 @@
         <v>45734.0</v>
       </c>
       <c r="D71" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="F71" s="23">
         <v>0.0</v>
@@ -2963,19 +2963,19 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="C72" s="6">
         <v>45734.0</v>
       </c>
       <c r="D72" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="F72" s="8">
         <v>0.0</v>
@@ -2983,19 +2983,19 @@
     </row>
     <row r="73">
       <c r="A73" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C73" s="21">
         <v>45734.0</v>
       </c>
       <c r="D73" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="F73" s="23">
         <v>0.0</v>
@@ -3006,7 +3006,7 @@
         <v>132</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="C74" s="6">
         <v>45734.0</v>
@@ -3015,18 +3015,18 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="F74" s="8">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="C75" s="21">
         <v>45734.0</v>
@@ -3035,29 +3035,29 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="F75" s="23">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B76" s="28" t="s">
+      <c r="A76" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="16">
+      <c r="C76" s="6">
         <v>45734.0</v>
       </c>
-      <c r="D76" s="17">
+      <c r="D76" s="7">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F76" s="31">
+      <c r="F76" s="8">
         <v>0.0</v>
       </c>
     </row>
@@ -3066,16 +3066,16 @@
         <v>136</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C77" s="21">
         <v>45734.0</v>
       </c>
       <c r="D77" s="22">
-        <v>0.8125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="F77" s="23">
         <v>0.0</v>
@@ -3083,79 +3083,79 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="C78" s="6">
         <v>45734.0</v>
       </c>
       <c r="D78" s="7">
-        <v>0.8125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="F78" s="8">
-        <v>65.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C79" s="21">
         <v>45734.0</v>
       </c>
       <c r="D79" s="22">
-        <v>0.8333333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="F79" s="23">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C80" s="6">
+      <c r="A80" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" s="16">
         <v>45734.0</v>
       </c>
-      <c r="D80" s="7">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F80" s="8">
+      <c r="D80" s="17">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F80" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="C81" s="21">
         <v>45734.0</v>
       </c>
       <c r="D81" s="22">
-        <v>0.8333333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F81" s="23">
         <v>0.0</v>
@@ -3163,59 +3163,59 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="C82" s="6">
         <v>45734.0</v>
       </c>
       <c r="D82" s="7">
-        <v>0.8541666666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="F82" s="8">
-        <v>7.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C83" s="21">
-        <v>45735.0</v>
+        <v>45734.0</v>
       </c>
       <c r="D83" s="22">
-        <v>0.4166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="F83" s="23">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="C84" s="6">
-        <v>45735.0</v>
+        <v>45734.0</v>
       </c>
       <c r="D84" s="7">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F84" s="8">
         <v>0.0</v>
@@ -3226,16 +3226,16 @@
         <v>148</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C85" s="21">
-        <v>45735.0</v>
+        <v>45734.0</v>
       </c>
       <c r="D85" s="22">
-        <v>0.5208333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="F85" s="23">
         <v>0.0</v>
@@ -3243,22 +3243,22 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="C86" s="6">
-        <v>45735.0</v>
+        <v>45734.0</v>
       </c>
       <c r="D86" s="7">
-        <v>0.5833333333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="F86" s="8">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="87">
@@ -3266,13 +3266,13 @@
         <v>151</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C87" s="21">
         <v>45735.0</v>
       </c>
       <c r="D87" s="22">
-        <v>0.625</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E87" s="20" t="s">
         <v>27</v>
@@ -3286,16 +3286,16 @@
         <v>152</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="C88" s="6">
         <v>45735.0</v>
       </c>
       <c r="D88" s="7">
-        <v>0.7083333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>153</v>
+        <v>32</v>
       </c>
       <c r="F88" s="8">
         <v>0.0</v>
@@ -3303,19 +3303,19 @@
     </row>
     <row r="89">
       <c r="A89" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="C89" s="21">
         <v>45735.0</v>
       </c>
       <c r="D89" s="22">
-        <v>0.7083333333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
       <c r="F89" s="23">
         <v>0.0</v>
@@ -3323,19 +3323,19 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="C90" s="6">
         <v>45735.0</v>
       </c>
       <c r="D90" s="7">
-        <v>0.75</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="F90" s="8">
         <v>0.0</v>
@@ -3343,19 +3343,19 @@
     </row>
     <row r="91">
       <c r="A91" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="C91" s="21">
         <v>45735.0</v>
       </c>
       <c r="D91" s="22">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>158</v>
+        <v>27</v>
       </c>
       <c r="F91" s="23">
         <v>0.0</v>
@@ -3363,19 +3363,19 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C92" s="6">
         <v>45735.0</v>
       </c>
       <c r="D92" s="7">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="F92" s="8">
         <v>0.0</v>
@@ -3383,19 +3383,19 @@
     </row>
     <row r="93">
       <c r="A93" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>161</v>
+        <v>7</v>
       </c>
       <c r="C93" s="21">
         <v>45735.0</v>
       </c>
       <c r="D93" s="22">
-        <v>0.7708333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="F93" s="23">
         <v>0.0</v>
@@ -3403,36 +3403,36 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="C94" s="6">
         <v>45735.0</v>
       </c>
       <c r="D94" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="F94" s="8">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="19" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="C95" s="21">
         <v>45735.0</v>
       </c>
       <c r="D95" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E95" s="20" t="s">
         <v>163</v>
@@ -3446,16 +3446,16 @@
         <v>164</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C96" s="6">
         <v>45735.0</v>
       </c>
       <c r="D96" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="F96" s="8">
         <v>0.0</v>
@@ -3466,13 +3466,13 @@
         <v>165</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C97" s="21">
         <v>45735.0</v>
       </c>
       <c r="D97" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E97" s="20" t="s">
         <v>49</v>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="C98" s="6">
         <v>45735.0</v>
@@ -3495,18 +3495,18 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F98" s="8">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="19" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C99" s="21">
         <v>45735.0</v>
@@ -3515,18 +3515,18 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="F99" s="23">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C100" s="6">
         <v>45735.0</v>
@@ -3535,18 +3535,18 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="F100" s="8">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="19" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="C101" s="21">
         <v>45735.0</v>
@@ -3555,115 +3555,115 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F101" s="23">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B102" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" s="16">
+      <c r="A102" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="6">
         <v>45735.0</v>
       </c>
-      <c r="D102" s="17">
-        <v>0.7958333333333333</v>
-      </c>
-      <c r="E102" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="F102" s="31">
+      <c r="D102" s="7">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F102" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="19" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C103" s="21">
         <v>45735.0</v>
       </c>
       <c r="D103" s="22">
-        <v>0.8125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="F103" s="23">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C104" s="6">
         <v>45735.0</v>
       </c>
       <c r="D104" s="7">
-        <v>0.8125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F104" s="8">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="19" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C105" s="21">
         <v>45735.0</v>
       </c>
       <c r="D105" s="22">
-        <v>0.8125</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E105" s="20" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F105" s="23">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C106" s="6">
+      <c r="A106" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B106" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" s="16">
         <v>45735.0</v>
       </c>
-      <c r="D106" s="7">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F106" s="8">
+      <c r="D106" s="17">
+        <v>0.7958333333333333</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F106" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="19" t="s">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="B107" s="20" t="s">
         <v>16</v>
@@ -3672,10 +3672,10 @@
         <v>45735.0</v>
       </c>
       <c r="D107" s="22">
-        <v>0.8333333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F107" s="23">
         <v>0.0</v>
@@ -3683,19 +3683,19 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C108" s="6">
         <v>45735.0</v>
       </c>
       <c r="D108" s="7">
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="F108" s="8">
         <v>0.0</v>
@@ -3703,107 +3703,107 @@
     </row>
     <row r="109">
       <c r="A109" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B109" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="21">
-        <v>45736.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D109" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F109" s="23">
         <v>0.0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B110" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" s="16">
-        <v>45736.0</v>
-      </c>
-      <c r="D110" s="17">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E110" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="F110" s="31">
+      <c r="A110" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C110" s="6">
+        <v>45735.0</v>
+      </c>
+      <c r="D110" s="7">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F110" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="19" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C111" s="21">
-        <v>45736.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D111" s="22">
-        <v>0.8125</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="F111" s="23">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="C112" s="6">
-        <v>45736.0</v>
+        <v>45735.0</v>
       </c>
       <c r="D112" s="7">
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="F112" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="B113" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C113" s="21">
-        <v>45736.0</v>
-      </c>
-      <c r="D113" s="22">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E113" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F113" s="23">
-        <v>0.0</v>
+      <c r="A113" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B113" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C113" s="31">
+        <v>45735.0</v>
+      </c>
+      <c r="D113" s="32">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E113" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="F113" s="33">
+        <v>6.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>7</v>
@@ -3812,53 +3812,53 @@
         <v>45736.0</v>
       </c>
       <c r="D114" s="7">
-        <v>0.8333333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="F114" s="8">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B115" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C115" s="21">
+      <c r="A115" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B115" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" s="11">
         <v>45736.0</v>
       </c>
-      <c r="D115" s="22">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E115" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="F115" s="23">
-        <v>10.0</v>
+      <c r="D115" s="12">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F115" s="33">
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="32" t="s">
-        <v>183</v>
+      <c r="A116" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C116" s="33">
+      <c r="C116" s="6">
         <v>45736.0</v>
       </c>
-      <c r="D116" s="34">
-        <v>0.8333333333333334</v>
+      <c r="D116" s="7">
+        <v>0.8125</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F116" s="35">
-        <v>20.0</v>
+        <v>109</v>
+      </c>
+      <c r="F116" s="8">
+        <v>10.0</v>
       </c>
     </row>
     <row r="117">
@@ -3872,10 +3872,10 @@
         <v>45736.0</v>
       </c>
       <c r="D117" s="22">
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F117" s="23">
         <v>0.0</v>
@@ -3886,99 +3886,99 @@
         <v>186</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="C118" s="6">
-        <v>45737.0</v>
+        <v>45736.0</v>
       </c>
       <c r="D118" s="7">
-        <v>0.4166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="F118" s="8">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>118</v>
+        <v>7</v>
       </c>
       <c r="C119" s="21">
-        <v>45737.0</v>
+        <v>45736.0</v>
       </c>
       <c r="D119" s="22">
-        <v>0.4305555555555556</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="F119" s="23">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="6">
+        <v>45736.0</v>
+      </c>
+      <c r="D120" s="7">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E120" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B120" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C120" s="6">
-        <v>45737.0</v>
-      </c>
-      <c r="D120" s="7">
-        <v>0.4375</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="F120" s="8">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="19" t="s">
-        <v>148</v>
+      <c r="A121" s="29" t="s">
+        <v>190</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C121" s="21">
-        <v>45737.0</v>
-      </c>
-      <c r="D121" s="22">
-        <v>0.625</v>
+        <v>7</v>
+      </c>
+      <c r="C121" s="31">
+        <v>45736.0</v>
+      </c>
+      <c r="D121" s="32">
+        <v>0.8333333333333334</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="F121" s="23">
-        <v>0.0</v>
+        <v>191</v>
+      </c>
+      <c r="F121" s="40">
+        <v>20.0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="C122" s="6">
-        <v>45737.0</v>
+        <v>45736.0</v>
       </c>
       <c r="D122" s="7">
-        <v>0.7291666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
       <c r="F122" s="8">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="123">
@@ -3986,36 +3986,36 @@
         <v>193</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="C123" s="21">
         <v>45737.0</v>
       </c>
       <c r="D123" s="22">
-        <v>0.75</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E123" s="20" t="s">
         <v>194</v>
       </c>
       <c r="F123" s="23">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="C124" s="6">
         <v>45737.0</v>
       </c>
       <c r="D124" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.4305555555555556</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="F124" s="8">
         <v>0.0</v>
@@ -4026,39 +4026,39 @@
         <v>196</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="C125" s="21">
         <v>45737.0</v>
       </c>
       <c r="D125" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.4375</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
       <c r="F125" s="23">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="C126" s="6">
         <v>45737.0</v>
       </c>
       <c r="D126" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="F126" s="8">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="127">
@@ -4066,19 +4066,19 @@
         <v>198</v>
       </c>
       <c r="B127" s="20" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="C127" s="21">
         <v>45737.0</v>
       </c>
       <c r="D127" s="22">
-        <v>0.7916666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E127" s="20" t="s">
         <v>199</v>
       </c>
       <c r="F127" s="23">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="128">
@@ -4086,116 +4086,116 @@
         <v>200</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="C128" s="6">
         <v>45737.0</v>
       </c>
       <c r="D128" s="7">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="F128" s="8">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="19" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="B129" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C129" s="21">
         <v>45737.0</v>
       </c>
       <c r="D129" s="22">
-        <v>0.8541666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="F129" s="23">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="s">
-        <v>61</v>
+        <v>203</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C130" s="6">
-        <v>45739.0</v>
+        <v>45737.0</v>
       </c>
       <c r="D130" s="7">
-        <v>0.5625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="F130" s="8">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="19" t="s">
-        <v>30</v>
+        <v>204</v>
       </c>
       <c r="B131" s="20" t="s">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="C131" s="21">
-        <v>45739.0</v>
+        <v>45737.0</v>
       </c>
       <c r="D131" s="22">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="F131" s="23">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="C132" s="6">
-        <v>45739.0</v>
+        <v>45737.0</v>
       </c>
       <c r="D132" s="7">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F132" s="8">
-        <v>25.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="19" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="C133" s="21">
-        <v>45739.0</v>
+        <v>45737.0</v>
       </c>
       <c r="D133" s="22">
-        <v>0.5833333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="F133" s="23">
         <v>10.0</v>
@@ -4203,159 +4203,159 @@
     </row>
     <row r="134">
       <c r="A134" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="C134" s="6">
-        <v>45739.0</v>
+        <v>45737.0</v>
       </c>
       <c r="D134" s="7">
-        <v>0.625</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="F134" s="8">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="B135" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C135" s="21">
-        <v>45739.0</v>
-      </c>
-      <c r="D135" s="22">
-        <v>0.625</v>
-      </c>
-      <c r="E135" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F135" s="23">
+      <c r="A135" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="B135" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C135" s="31">
+        <v>45737.0</v>
+      </c>
+      <c r="D135" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E135" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F135" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="6">
-        <v>45739.0</v>
-      </c>
-      <c r="D136" s="7">
-        <v>0.625</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F136" s="8">
+      <c r="A136" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B136" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C136" s="26">
+        <v>45738.0</v>
+      </c>
+      <c r="D136" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E136" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F136" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="19" t="s">
-        <v>206</v>
+        <v>67</v>
       </c>
       <c r="B137" s="20" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="C137" s="21">
         <v>45739.0</v>
       </c>
       <c r="D137" s="22">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="F137" s="23">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="C138" s="6">
         <v>45739.0</v>
       </c>
       <c r="D138" s="7">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="F138" s="8">
         <v>0.0</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B139" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" s="11">
+      <c r="A139" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B139" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C139" s="21">
         <v>45739.0</v>
       </c>
-      <c r="D139" s="12">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E139" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F139" s="26">
-        <v>0.0</v>
+      <c r="D139" s="22">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E139" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F139" s="23">
+        <v>25.0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="s">
-        <v>69</v>
+        <v>205</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="C140" s="6">
         <v>45739.0</v>
       </c>
       <c r="D140" s="7">
-        <v>0.75</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="F140" s="8">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="19" t="s">
-        <v>72</v>
+        <v>213</v>
       </c>
       <c r="B141" s="20" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="C141" s="21">
         <v>45739.0</v>
       </c>
       <c r="D141" s="22">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="F141" s="23">
         <v>0.0</v>
@@ -4363,19 +4363,19 @@
     </row>
     <row r="142">
       <c r="A142" s="4" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="C142" s="6">
         <v>45739.0</v>
       </c>
       <c r="D142" s="7">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="F142" s="8">
         <v>0.0</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="143">
       <c r="A143" s="19" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B143" s="20" t="s">
         <v>7</v>
@@ -4392,90 +4392,90 @@
         <v>45739.0</v>
       </c>
       <c r="D143" s="22">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
       <c r="E143" s="20" t="s">
-        <v>209</v>
+        <v>52</v>
       </c>
       <c r="F143" s="23">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
       <c r="C144" s="6">
         <v>45739.0</v>
       </c>
       <c r="D144" s="7">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="F144" s="8">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="19" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="C145" s="21">
         <v>45739.0</v>
       </c>
       <c r="D145" s="22">
-        <v>0.8541666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E145" s="20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F145" s="23">
         <v>0.0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="6">
+      <c r="A146" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B146" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" s="16">
         <v>45739.0</v>
       </c>
-      <c r="D146" s="7">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F146" s="8">
-        <v>7.0</v>
+      <c r="D146" s="17">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E146" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F146" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B147" s="20" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C147" s="21">
-        <v>45740.0</v>
+        <v>45739.0</v>
       </c>
       <c r="D147" s="22">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="E147" s="20" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F147" s="23">
         <v>0.0</v>
@@ -4483,19 +4483,19 @@
     </row>
     <row r="148">
       <c r="A148" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="C148" s="6">
-        <v>45740.0</v>
+        <v>45739.0</v>
       </c>
       <c r="D148" s="7">
-        <v>0.4166666666666667</v>
+        <v>0.75</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>212</v>
+        <v>71</v>
       </c>
       <c r="F148" s="8">
         <v>0.0</v>
@@ -4503,19 +4503,19 @@
     </row>
     <row r="149">
       <c r="A149" s="19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B149" s="20" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C149" s="21">
-        <v>45740.0</v>
+        <v>45739.0</v>
       </c>
       <c r="D149" s="22">
-        <v>0.4375</v>
+        <v>0.8125</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F149" s="23">
         <v>0.0</v>
@@ -4523,59 +4523,59 @@
     </row>
     <row r="150">
       <c r="A150" s="4" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="C150" s="6">
-        <v>45740.0</v>
+        <v>45739.0</v>
       </c>
       <c r="D150" s="7">
-        <v>0.4791666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F150" s="8">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B151" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="21">
+        <v>45739.0</v>
+      </c>
+      <c r="D151" s="22">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E151" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C151" s="21">
-        <v>45740.0</v>
-      </c>
-      <c r="D151" s="22">
-        <v>0.6875</v>
-      </c>
-      <c r="E151" s="20" t="s">
-        <v>39</v>
-      </c>
       <c r="F151" s="23">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C152" s="6">
-        <v>45740.0</v>
+        <v>45739.0</v>
       </c>
       <c r="D152" s="7">
-        <v>0.7916666666666666</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="F152" s="8">
         <v>0.0</v>
@@ -4583,1781 +4583,1781 @@
     </row>
     <row r="153">
       <c r="A153" s="19" t="s">
-        <v>97</v>
+        <v>220</v>
       </c>
       <c r="B153" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C153" s="21">
+        <v>45739.0</v>
+      </c>
+      <c r="D153" s="22">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F153" s="23">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C154" s="26">
+        <v>45739.0</v>
+      </c>
+      <c r="D154" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E154" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F154" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B155" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" s="21">
         <v>45740.0</v>
       </c>
-      <c r="D153" s="22">
+      <c r="D155" s="22">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E155" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F155" s="23">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C156" s="6">
+        <v>45740.0</v>
+      </c>
+      <c r="D156" s="7">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F156" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B157" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C157" s="21">
+        <v>45740.0</v>
+      </c>
+      <c r="D157" s="22">
+        <v>0.4375</v>
+      </c>
+      <c r="E157" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F157" s="23">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C158" s="6">
+        <v>45740.0</v>
+      </c>
+      <c r="D158" s="7">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F158" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B159" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C159" s="21">
+        <v>45740.0</v>
+      </c>
+      <c r="D159" s="22">
+        <v>0.6875</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F159" s="23">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" s="6">
+        <v>45740.0</v>
+      </c>
+      <c r="D160" s="7">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E153" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="F153" s="23">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B154" s="28" t="s">
+      <c r="E160" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F160" s="8">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B161" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="21">
+        <v>45740.0</v>
+      </c>
+      <c r="D161" s="22">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E161" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F161" s="23">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B162" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C154" s="29">
+      <c r="C162" s="36">
         <v>45740.0</v>
       </c>
-      <c r="D154" s="30">
+      <c r="D162" s="37">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E154" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F154" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B155" s="25" t="s">
+      <c r="E162" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F162" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B163" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C163" s="11">
         <v>45741.0</v>
       </c>
-      <c r="D155" s="12">
+      <c r="D163" s="12">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E155" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="F155" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B156" s="28" t="s">
+      <c r="E163" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F163" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B164" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C164" s="26">
+        <v>45741.0</v>
+      </c>
+      <c r="D164" s="27">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E164" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F164" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B165" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C156" s="16">
+      <c r="C165" s="11">
         <v>45742.0</v>
       </c>
-      <c r="D156" s="17">
+      <c r="D165" s="12">
         <v>0.7958333333333333</v>
       </c>
-      <c r="E156" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="F156" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="B157" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C157" s="37">
-        <v>45742.0</v>
-      </c>
-      <c r="D157" s="38">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E157" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F157" s="39">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B158" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" s="16">
-        <v>45743.0</v>
-      </c>
-      <c r="D158" s="17">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E158" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="F158" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="B159" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C159" s="37">
-        <v>45743.0</v>
-      </c>
-      <c r="D159" s="38">
-        <v>0.875</v>
-      </c>
-      <c r="E159" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F159" s="39">
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B160" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" s="16">
-        <v>45746.0</v>
-      </c>
-      <c r="D160" s="17">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E160" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F160" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B161" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" s="40">
-        <v>45747.0</v>
-      </c>
-      <c r="D161" s="41">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E161" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F161" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B162" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" s="16">
-        <v>45748.0</v>
-      </c>
-      <c r="D162" s="17">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E162" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F162" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="B163" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" s="37">
-        <v>45749.0</v>
-      </c>
-      <c r="D163" s="38">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E163" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F163" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B164" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" s="16">
-        <v>45749.0</v>
-      </c>
-      <c r="D164" s="17">
-        <v>0.7958333333333333</v>
-      </c>
-      <c r="E164" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="F164" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B165" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" s="11">
-        <v>45750.0</v>
-      </c>
-      <c r="D165" s="12">
-        <v>0.7916666666666666</v>
-      </c>
       <c r="E165" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F165" s="26">
+        <v>225</v>
+      </c>
+      <c r="F165" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="32" t="s">
-        <v>220</v>
+      <c r="A166" s="24" t="s">
+        <v>226</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C166" s="33">
-        <v>45750.0</v>
-      </c>
-      <c r="D166" s="34">
+      <c r="C166" s="26">
+        <v>45742.0</v>
+      </c>
+      <c r="D166" s="27">
         <v>0.8333333333333334</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F166" s="31">
-        <v>0.0</v>
+        <v>138</v>
+      </c>
+      <c r="F166" s="41">
+        <v>10.0</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="B167" s="20" t="s">
+      <c r="A167" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="B167" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C167" s="31">
+        <v>45742.0</v>
+      </c>
+      <c r="D167" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E167" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F167" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B168" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" s="16">
+        <v>45743.0</v>
+      </c>
+      <c r="D168" s="17">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E168" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F168" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="B169" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C167" s="37">
-        <v>45750.0</v>
-      </c>
-      <c r="D167" s="38">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E167" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F167" s="39">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B168" s="28" t="s">
+      <c r="C169" s="31">
+        <v>45743.0</v>
+      </c>
+      <c r="D169" s="32">
+        <v>0.875</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F169" s="40">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B170" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C170" s="26">
+        <v>45744.0</v>
+      </c>
+      <c r="D170" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="E170" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="F170" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="B171" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C171" s="31">
+        <v>45744.0</v>
+      </c>
+      <c r="D171" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E171" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F171" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B172" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C172" s="26">
+        <v>45745.0</v>
+      </c>
+      <c r="D172" s="27">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E172" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F172" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B173" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C168" s="16">
-        <v>45753.0</v>
-      </c>
-      <c r="D168" s="17">
+      <c r="C173" s="11">
+        <v>45746.0</v>
+      </c>
+      <c r="D173" s="12">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E168" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F168" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B169" s="25" t="s">
+      <c r="E173" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F173" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B174" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C174" s="26">
+        <v>45746.0</v>
+      </c>
+      <c r="D174" s="27">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E174" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F174" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B175" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C169" s="40">
-        <v>45754.0</v>
-      </c>
-      <c r="D169" s="41">
+      <c r="C175" s="42">
+        <v>45747.0</v>
+      </c>
+      <c r="D175" s="43">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E169" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F169" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B170" s="28" t="s">
+      <c r="E175" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F175" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B176" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C170" s="16">
-        <v>45755.0</v>
-      </c>
-      <c r="D170" s="17">
+      <c r="C176" s="16">
+        <v>45748.0</v>
+      </c>
+      <c r="D176" s="17">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E170" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F170" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="B171" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C171" s="37">
-        <v>45755.0</v>
-      </c>
-      <c r="D171" s="38">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E171" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F171" s="39">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B172" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" s="16">
-        <v>45756.0</v>
-      </c>
-      <c r="D172" s="17">
-        <v>0.7958333333333333</v>
-      </c>
-      <c r="E172" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="F172" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B173" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" s="11">
-        <v>45757.0</v>
-      </c>
-      <c r="D173" s="12">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E173" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F173" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="33">
-        <v>45757.0</v>
-      </c>
-      <c r="D174" s="34">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F174" s="35">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B175" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" s="11">
-        <v>45760.0</v>
-      </c>
-      <c r="D175" s="12">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E175" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F175" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B176" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" s="29">
-        <v>45761.0</v>
-      </c>
-      <c r="D176" s="30">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E176" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F176" s="31">
+      <c r="E176" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F176" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B177" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" s="11">
-        <v>45762.0</v>
-      </c>
-      <c r="D177" s="12">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E177" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="F177" s="26">
+      <c r="A177" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="B177" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C177" s="31">
+        <v>45748.0</v>
+      </c>
+      <c r="D177" s="32">
+        <v>0.625</v>
+      </c>
+      <c r="E177" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F177" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="32" t="s">
-        <v>225</v>
+      <c r="A178" s="24" t="s">
+        <v>233</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C178" s="33">
-        <v>45762.0</v>
-      </c>
-      <c r="D178" s="34">
-        <v>0.8333333333333334</v>
+      <c r="C178" s="26">
+        <v>45749.0</v>
+      </c>
+      <c r="D178" s="27">
+        <v>0.7916666666666666</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F178" s="35">
-        <v>32.0</v>
+        <v>138</v>
+      </c>
+      <c r="F178" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B179" s="25" t="s">
+      <c r="A179" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B179" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C179" s="11">
-        <v>45763.0</v>
+        <v>45749.0</v>
       </c>
       <c r="D179" s="12">
         <v>0.7958333333333333</v>
       </c>
       <c r="E179" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F179" s="26">
+        <v>234</v>
+      </c>
+      <c r="F179" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C180" s="33">
-        <v>45763.0</v>
-      </c>
-      <c r="D180" s="34">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F180" s="35">
-        <v>25.0</v>
+      <c r="A180" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="B180" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C180" s="26">
+        <v>45749.0</v>
+      </c>
+      <c r="D180" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E180" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F180" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B181" s="25" t="s">
+      <c r="A181" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B181" s="39" t="s">
         <v>16</v>
       </c>
       <c r="C181" s="11">
-        <v>45764.0</v>
+        <v>45750.0</v>
       </c>
       <c r="D181" s="12">
         <v>0.7916666666666666</v>
       </c>
       <c r="E181" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F181" s="26">
+        <v>183</v>
+      </c>
+      <c r="F181" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="32" t="s">
-        <v>228</v>
+      <c r="A182" s="24" t="s">
+        <v>236</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C182" s="33">
-        <v>45765.0</v>
-      </c>
-      <c r="D182" s="34">
+      <c r="C182" s="26">
+        <v>45750.0</v>
+      </c>
+      <c r="D182" s="27">
         <v>0.8333333333333334</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F182" s="35">
-        <v>15.0</v>
+        <v>138</v>
+      </c>
+      <c r="F182" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="36" t="s">
-        <v>229</v>
+      <c r="A183" s="29" t="s">
+        <v>237</v>
       </c>
       <c r="B183" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C183" s="37">
-        <v>45766.0</v>
-      </c>
-      <c r="D183" s="38">
-        <v>0.8125</v>
+      <c r="C183" s="31">
+        <v>45750.0</v>
+      </c>
+      <c r="D183" s="32">
+        <v>0.8333333333333334</v>
       </c>
       <c r="E183" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F183" s="39">
-        <v>20.0</v>
+        <v>191</v>
+      </c>
+      <c r="F183" s="40">
+        <v>25.0</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B184" s="28" t="s">
+      <c r="A184" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B184" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C184" s="26">
+        <v>45751.0</v>
+      </c>
+      <c r="D184" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E184" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F184" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B185" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C185" s="31">
+        <v>45752.0</v>
+      </c>
+      <c r="D185" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E185" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F185" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B186" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C184" s="16">
-        <v>45767.0</v>
-      </c>
-      <c r="D184" s="17">
+      <c r="C186" s="16">
+        <v>45753.0</v>
+      </c>
+      <c r="D186" s="17">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E184" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F184" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B185" s="25" t="s">
+      <c r="E186" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F186" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B187" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C187" s="31">
+        <v>45753.0</v>
+      </c>
+      <c r="D187" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E187" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F187" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B188" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C185" s="40">
-        <v>45768.0</v>
-      </c>
-      <c r="D185" s="41">
+      <c r="C188" s="36">
+        <v>45754.0</v>
+      </c>
+      <c r="D188" s="37">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E185" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F185" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B186" s="28" t="s">
+      <c r="E188" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F188" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B189" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C186" s="16">
-        <v>45769.0</v>
-      </c>
-      <c r="D186" s="17">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E186" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F186" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B187" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" s="11">
-        <v>45770.0</v>
-      </c>
-      <c r="D187" s="12">
-        <v>0.7958333333333333</v>
-      </c>
-      <c r="E187" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F187" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C188" s="33">
-        <v>45770.0</v>
-      </c>
-      <c r="D188" s="34">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F188" s="35">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B189" s="25" t="s">
-        <v>16</v>
-      </c>
       <c r="C189" s="11">
-        <v>45771.0</v>
+        <v>45755.0</v>
       </c>
       <c r="D189" s="12">
         <v>0.7916666666666666</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F189" s="26">
+        <v>140</v>
+      </c>
+      <c r="F189" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="32" t="s">
-        <v>232</v>
+      <c r="A190" s="24" t="s">
+        <v>239</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C190" s="33">
-        <v>45773.0</v>
-      </c>
-      <c r="D190" s="34">
+      <c r="C190" s="26">
+        <v>45755.0</v>
+      </c>
+      <c r="D190" s="27">
         <v>0.8333333333333334</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F190" s="35">
-        <v>25.0</v>
+        <v>138</v>
+      </c>
+      <c r="F190" s="41">
+        <v>8.0</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B191" s="25" t="s">
+      <c r="A191" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="B191" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C191" s="31">
+        <v>45755.0</v>
+      </c>
+      <c r="D191" s="32">
+        <v>0.625</v>
+      </c>
+      <c r="E191" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F191" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B192" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C191" s="11">
-        <v>45774.0</v>
-      </c>
-      <c r="D191" s="12">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E191" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F191" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B192" s="28" t="s">
+      <c r="C192" s="16">
+        <v>45756.0</v>
+      </c>
+      <c r="D192" s="17">
+        <v>0.7958333333333333</v>
+      </c>
+      <c r="E192" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F192" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="B193" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C193" s="31">
+        <v>45756.0</v>
+      </c>
+      <c r="D193" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E193" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F193" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B194" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C192" s="29">
-        <v>45775.0</v>
-      </c>
-      <c r="D192" s="30">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E192" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="F192" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="B193" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C193" s="37">
-        <v>45775.0</v>
-      </c>
-      <c r="D193" s="38">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E193" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F193" s="39">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B194" s="28" t="s">
-        <v>16</v>
-      </c>
       <c r="C194" s="16">
-        <v>45776.0</v>
+        <v>45757.0</v>
       </c>
       <c r="D194" s="17">
         <v>0.7916666666666666</v>
       </c>
       <c r="E194" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F194" s="31">
+        <v>183</v>
+      </c>
+      <c r="F194" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B195" s="25" t="s">
+      <c r="A195" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="B195" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="31">
+        <v>45757.0</v>
+      </c>
+      <c r="D195" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E195" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F195" s="40">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B196" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C196" s="26">
+        <v>45758.0</v>
+      </c>
+      <c r="D196" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E196" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F196" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="B197" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C197" s="31">
+        <v>45759.0</v>
+      </c>
+      <c r="D197" s="32">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E197" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="F197" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B198" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C198" s="26">
+        <v>45759.0</v>
+      </c>
+      <c r="D198" s="27">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E198" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F198" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B199" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C195" s="11">
-        <v>45777.0</v>
-      </c>
-      <c r="D195" s="12">
-        <v>0.7958333333333333</v>
-      </c>
-      <c r="E195" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F195" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C196" s="33">
-        <v>45777.0</v>
-      </c>
-      <c r="D196" s="34">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F196" s="35">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B197" s="25" t="s">
+      <c r="C199" s="11">
+        <v>45760.0</v>
+      </c>
+      <c r="D199" s="12">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E199" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F199" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B200" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C200" s="26">
+        <v>45760.0</v>
+      </c>
+      <c r="D200" s="27">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E200" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F200" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B201" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C197" s="11">
-        <v>45778.0</v>
-      </c>
-      <c r="D197" s="12">
+      <c r="C201" s="42">
+        <v>45761.0</v>
+      </c>
+      <c r="D201" s="43">
         <v>0.7916666666666666</v>
       </c>
-      <c r="E197" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F197" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C198" s="33">
-        <v>45778.0</v>
-      </c>
-      <c r="D198" s="34">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F198" s="35">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="B199" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C199" s="37">
-        <v>45779.0</v>
-      </c>
-      <c r="D199" s="38">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E199" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F199" s="39">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B200" s="28" t="s">
+      <c r="E201" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F201" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B202" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C200" s="16">
-        <v>45781.0</v>
-      </c>
-      <c r="D200" s="17">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E200" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F200" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B201" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" s="40">
-        <v>45782.0</v>
-      </c>
-      <c r="D201" s="41">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E201" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="F201" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B202" s="28" t="s">
-        <v>16</v>
-      </c>
       <c r="C202" s="16">
-        <v>45783.0</v>
+        <v>45762.0</v>
       </c>
       <c r="D202" s="17">
         <v>0.7916666666666666</v>
       </c>
       <c r="E202" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F202" s="31">
+        <v>140</v>
+      </c>
+      <c r="F202" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B203" s="25" t="s">
+      <c r="A203" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="B203" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" s="31">
+        <v>45762.0</v>
+      </c>
+      <c r="D203" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E203" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F203" s="40">
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B204" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C203" s="11">
-        <v>45784.0</v>
-      </c>
-      <c r="D203" s="12">
+      <c r="C204" s="16">
+        <v>45763.0</v>
+      </c>
+      <c r="D204" s="17">
         <v>0.7958333333333333</v>
       </c>
-      <c r="E203" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F203" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B204" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C204" s="16">
-        <v>45785.0</v>
-      </c>
-      <c r="D204" s="17">
-        <v>0.7916666666666666</v>
-      </c>
       <c r="E204" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="F204" s="31">
+        <v>248</v>
+      </c>
+      <c r="F204" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="36" t="s">
-        <v>239</v>
+      <c r="A205" s="29" t="s">
+        <v>249</v>
       </c>
       <c r="B205" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C205" s="37">
+      <c r="C205" s="31">
+        <v>45763.0</v>
+      </c>
+      <c r="D205" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E205" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F205" s="40">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B206" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C206" s="16">
+        <v>45764.0</v>
+      </c>
+      <c r="D206" s="17">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E206" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F206" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="B207" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C207" s="31">
+        <v>45765.0</v>
+      </c>
+      <c r="D207" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E207" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F207" s="40">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B208" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C208" s="26">
+        <v>45765.0</v>
+      </c>
+      <c r="D208" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E208" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F208" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="B209" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209" s="31">
+        <v>45766.0</v>
+      </c>
+      <c r="D209" s="32">
+        <v>0.8125</v>
+      </c>
+      <c r="E209" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F209" s="40">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B210" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C210" s="26">
+        <v>45766.0</v>
+      </c>
+      <c r="D210" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E210" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F210" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B211" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C211" s="11">
+        <v>45767.0</v>
+      </c>
+      <c r="D211" s="12">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E211" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F211" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B212" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C212" s="26">
+        <v>45767.0</v>
+      </c>
+      <c r="D212" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E212" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="F212" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B213" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C213" s="42">
+        <v>45768.0</v>
+      </c>
+      <c r="D213" s="43">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E213" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F213" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B214" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C214" s="16">
+        <v>45769.0</v>
+      </c>
+      <c r="D214" s="17">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E214" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F214" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B215" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C215" s="11">
+        <v>45770.0</v>
+      </c>
+      <c r="D215" s="12">
+        <v>0.7958333333333333</v>
+      </c>
+      <c r="E215" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F215" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" s="26">
+        <v>45770.0</v>
+      </c>
+      <c r="D216" s="27">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F216" s="41">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B217" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217" s="11">
+        <v>45771.0</v>
+      </c>
+      <c r="D217" s="12">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F217" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="B218" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C218" s="26">
+        <v>45771.0</v>
+      </c>
+      <c r="D218" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E218" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F218" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="B219" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C219" s="31">
+        <v>45772.0</v>
+      </c>
+      <c r="D219" s="32">
+        <v>0.75</v>
+      </c>
+      <c r="E219" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F219" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="26">
+        <v>45773.0</v>
+      </c>
+      <c r="D220" s="27">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F220" s="41">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="B221" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C221" s="31">
+        <v>45773.0</v>
+      </c>
+      <c r="D221" s="32">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E221" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F221" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B222" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C222" s="16">
+        <v>45774.0</v>
+      </c>
+      <c r="D222" s="17">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E222" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F222" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B223" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C223" s="42">
+        <v>45775.0</v>
+      </c>
+      <c r="D223" s="43">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E223" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F223" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" s="26">
+        <v>45775.0</v>
+      </c>
+      <c r="D224" s="27">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F224" s="41">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B225" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C225" s="11">
+        <v>45776.0</v>
+      </c>
+      <c r="D225" s="12">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E225" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="F225" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B226" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C226" s="26">
+        <v>45776.0</v>
+      </c>
+      <c r="D226" s="27">
+        <v>0.625</v>
+      </c>
+      <c r="E226" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F226" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B227" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C227" s="11">
+        <v>45777.0</v>
+      </c>
+      <c r="D227" s="12">
+        <v>0.7958333333333333</v>
+      </c>
+      <c r="E227" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F227" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" s="26">
+        <v>45777.0</v>
+      </c>
+      <c r="D228" s="27">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F228" s="41">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B229" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C229" s="11">
+        <v>45778.0</v>
+      </c>
+      <c r="D229" s="12">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E229" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F229" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C230" s="26">
+        <v>45778.0</v>
+      </c>
+      <c r="D230" s="27">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F230" s="41">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="29" t="s">
+        <v>262</v>
+      </c>
+      <c r="B231" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" s="31">
+        <v>45779.0</v>
+      </c>
+      <c r="D231" s="32">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E231" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F231" s="40">
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B232" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C232" s="16">
+        <v>45781.0</v>
+      </c>
+      <c r="D232" s="17">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E232" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F232" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B233" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C233" s="42">
+        <v>45782.0</v>
+      </c>
+      <c r="D233" s="43">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E233" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F233" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B234" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C234" s="16">
+        <v>45783.0</v>
+      </c>
+      <c r="D234" s="17">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E234" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F234" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="B235" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C235" s="11">
+        <v>45784.0</v>
+      </c>
+      <c r="D235" s="12">
+        <v>0.7958333333333333</v>
+      </c>
+      <c r="E235" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F235" s="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B236" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C236" s="16">
+        <v>45785.0</v>
+      </c>
+      <c r="D236" s="17">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E236" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F236" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B237" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" s="31">
         <v>45790.0</v>
       </c>
-      <c r="D205" s="38">
+      <c r="D237" s="32">
         <v>0.8125</v>
       </c>
-      <c r="E205" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="F205" s="39">
+      <c r="E237" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F237" s="40">
         <v>26.5</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="B206" s="5" t="s">
+    <row r="238">
+      <c r="A238" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B238" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C238" s="26">
+        <v>45792.0</v>
+      </c>
+      <c r="D238" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E238" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F238" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="B239" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C206" s="33">
+      <c r="C239" s="31">
         <v>45793.0</v>
       </c>
-      <c r="D206" s="34">
+      <c r="D239" s="32">
         <v>0.75</v>
       </c>
-      <c r="E206" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F206" s="35">
+      <c r="E239" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F239" s="40">
         <v>27.5</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="36" t="s">
-        <v>241</v>
-      </c>
-      <c r="B207" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C207" s="37">
-        <v>45731.0</v>
-      </c>
-      <c r="D207" s="38">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E207" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="F207" s="26">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="B208" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C208" s="33">
-        <v>45731.0</v>
-      </c>
-      <c r="D208" s="34">
+    <row r="240">
+      <c r="A240" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B240" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C240" s="26">
+        <v>45793.0</v>
+      </c>
+      <c r="D240" s="27">
+        <v>0.75</v>
+      </c>
+      <c r="E240" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F240" s="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B241" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C241" s="31">
+        <v>45794.0</v>
+      </c>
+      <c r="D241" s="32">
         <v>0.5833333333333334</v>
       </c>
-      <c r="E208" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F208" s="31">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="B209" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C209" s="37">
-        <v>45735.0</v>
-      </c>
-      <c r="D209" s="38">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E209" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="F209" s="26">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="B210" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C210" s="33">
-        <v>45744.0</v>
-      </c>
-      <c r="D210" s="34">
-        <v>0.5</v>
-      </c>
-      <c r="E210" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="F210" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="B211" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C211" s="37">
-        <v>45759.0</v>
-      </c>
-      <c r="D211" s="38">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E211" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="F211" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="B212" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C212" s="33">
-        <v>45731.0</v>
-      </c>
-      <c r="D212" s="34">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E212" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F212" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="36" t="s">
-        <v>251</v>
-      </c>
-      <c r="B213" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C213" s="37">
-        <v>45732.0</v>
-      </c>
-      <c r="D213" s="38">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E213" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F213" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="B214" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C214" s="33">
-        <v>45741.0</v>
-      </c>
-      <c r="D214" s="34">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E214" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F214" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B215" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C215" s="37">
-        <v>45744.0</v>
-      </c>
-      <c r="D215" s="38">
-        <v>0.75</v>
-      </c>
-      <c r="E215" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F215" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="B216" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C216" s="33">
-        <v>45745.0</v>
-      </c>
-      <c r="D216" s="34">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E216" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F216" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B217" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C217" s="37">
-        <v>45746.0</v>
-      </c>
-      <c r="D217" s="38">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E217" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F217" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="B218" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C218" s="33">
-        <v>45748.0</v>
-      </c>
-      <c r="D218" s="34">
-        <v>0.625</v>
-      </c>
-      <c r="E218" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F218" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="36" t="s">
-        <v>255</v>
-      </c>
-      <c r="B219" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C219" s="37">
-        <v>45755.0</v>
-      </c>
-      <c r="D219" s="38">
-        <v>0.625</v>
-      </c>
-      <c r="E219" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F219" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="B220" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C220" s="33">
-        <v>45758.0</v>
-      </c>
-      <c r="D220" s="34">
-        <v>0.75</v>
-      </c>
-      <c r="E220" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F220" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="B221" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C221" s="37">
-        <v>45759.0</v>
-      </c>
-      <c r="D221" s="38">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E221" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F221" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="B222" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C222" s="33">
-        <v>45760.0</v>
-      </c>
-      <c r="D222" s="34">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E222" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F222" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="B223" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C223" s="37">
-        <v>45771.0</v>
-      </c>
-      <c r="D223" s="38">
-        <v>0.75</v>
-      </c>
-      <c r="E223" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F223" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="B224" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C224" s="33">
-        <v>45772.0</v>
-      </c>
-      <c r="D224" s="34">
-        <v>0.75</v>
-      </c>
-      <c r="E224" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F224" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="B225" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C225" s="37">
-        <v>45773.0</v>
-      </c>
-      <c r="D225" s="38">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E225" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F225" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="B226" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C226" s="33">
-        <v>45776.0</v>
-      </c>
-      <c r="D226" s="34">
-        <v>0.625</v>
-      </c>
-      <c r="E226" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F226" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="B227" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C227" s="37">
-        <v>45792.0</v>
-      </c>
-      <c r="D227" s="38">
-        <v>0.75</v>
-      </c>
-      <c r="E227" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F227" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="B228" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C228" s="33">
-        <v>45793.0</v>
-      </c>
-      <c r="D228" s="34">
-        <v>0.75</v>
-      </c>
-      <c r="E228" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="F228" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="36" t="s">
-        <v>259</v>
-      </c>
-      <c r="B229" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C229" s="37">
-        <v>45794.0</v>
-      </c>
-      <c r="D229" s="38">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E229" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="F229" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="B230" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C230" s="33">
-        <v>45737.0</v>
-      </c>
-      <c r="D230" s="34">
-        <v>0.75</v>
-      </c>
-      <c r="E230" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F230" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="B231" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C231" s="37">
-        <v>45738.0</v>
-      </c>
-      <c r="D231" s="38">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E231" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="F231" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="B232" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C232" s="33">
-        <v>45739.0</v>
-      </c>
-      <c r="D232" s="34">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="E232" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F232" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="B233" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C233" s="37">
-        <v>45742.0</v>
-      </c>
-      <c r="D233" s="38">
-        <v>0.875</v>
-      </c>
-      <c r="E233" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="F233" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="B234" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C234" s="33">
-        <v>45749.0</v>
-      </c>
-      <c r="D234" s="34">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="E234" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F234" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="B235" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C235" s="37">
-        <v>45751.0</v>
-      </c>
-      <c r="D235" s="38">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="E235" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="F235" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="B236" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C236" s="33">
-        <v>45752.0</v>
-      </c>
-      <c r="D236" s="34">
-        <v>1.0</v>
-      </c>
-      <c r="E236" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F236" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="B237" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C237" s="37">
-        <v>45753.0</v>
-      </c>
-      <c r="D237" s="38">
-        <v>1.0416666666666667</v>
-      </c>
-      <c r="E237" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="F237" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="B238" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C238" s="33">
-        <v>45756.0</v>
-      </c>
-      <c r="D238" s="34">
-        <v>1.0833333333333333</v>
-      </c>
-      <c r="E238" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F238" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="B239" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C239" s="37">
-        <v>45765.0</v>
-      </c>
-      <c r="D239" s="38">
-        <v>1.125</v>
-      </c>
-      <c r="E239" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="F239" s="26">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="B240" s="43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C240" s="33">
-        <v>45766.0</v>
-      </c>
-      <c r="D240" s="34">
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="E240" s="43" t="s">
-        <v>261</v>
-      </c>
-      <c r="F240" s="31">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="B241" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C241" s="37">
-        <v>45767.0</v>
-      </c>
-      <c r="D241" s="38">
-        <v>1.2083333333333333</v>
-      </c>
-      <c r="E241" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="F241" s="26">
+      <c r="E241" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F241" s="33">
         <v>0.0</v>
       </c>
     </row>
@@ -12552,7 +12552,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
@@ -12571,10 +12571,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="25" t="s">
         <v>272</v>
       </c>
       <c r="C2" s="45"/>
@@ -12583,11 +12583,11 @@
       <c r="F2" s="59"/>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="B3" s="42" t="s">
-        <v>184</v>
+      <c r="B3" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="C3" s="50"/>
       <c r="D3" s="50"/>
@@ -12595,10 +12595,10 @@
       <c r="F3" s="60"/>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="25" t="s">
         <v>275</v>
       </c>
       <c r="C4" s="45"/>
@@ -12607,8 +12607,8 @@
       <c r="F4" s="59"/>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="s">
-        <v>168</v>
+      <c r="A5" s="29" t="s">
+        <v>173</v>
       </c>
       <c r="B5" s="50"/>
       <c r="C5" s="50"/>
@@ -12617,7 +12617,7 @@
       <c r="F5" s="60"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="24" t="s">
         <v>276</v>
       </c>
       <c r="B6" s="45"/>

--- a/athens_events.xlsx
+++ b/athens_events.xlsx
@@ -8,21 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sam/Desktop/athens-events-chatbot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31C6C29-AA59-7941-AB69-79591883F711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6E6DD7-0745-154D-B3CD-AEA0E43ED708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t>Event</t>
   </si>
@@ -48,9 +46,6 @@
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Trivia</t>
-  </si>
-  <si>
     <t>Comedy</t>
   </si>
   <si>
@@ -60,46 +55,10 @@
     <t>Marigold Farmers Market</t>
   </si>
   <si>
-    <t>Local 706</t>
-  </si>
-  <si>
-    <t>Georgia Theatre</t>
-  </si>
-  <si>
     <t>Winterville Cultural Center</t>
   </si>
   <si>
     <t>Marigold Auditorium</t>
-  </si>
-  <si>
-    <t>Column 3</t>
-  </si>
-  <si>
-    <t>Column 4</t>
-  </si>
-  <si>
-    <t>Column 5</t>
-  </si>
-  <si>
-    <t>Column 6</t>
-  </si>
-  <si>
-    <t>Southern Brewing</t>
-  </si>
-  <si>
-    <t>40 Watt</t>
-  </si>
-  <si>
-    <t>Dooleys</t>
-  </si>
-  <si>
-    <t>Akademia</t>
-  </si>
-  <si>
-    <t>Classic Center</t>
-  </si>
-  <si>
-    <t>Johnnys</t>
   </si>
   <si>
     <t>Pittard Park</t>
@@ -841,20 +800,6 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:F15">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Trivia"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Music"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column 3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column 4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Column 5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Column 6"/>
-  </tableColumns>
-  <tableStyleInfo name="Sheet2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -1052,15 +997,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF2DEEC-F15E-5245-B56D-4975DF715646}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1096,10 +1032,10 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="88" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="77">
         <v>45824</v>
@@ -1108,7 +1044,7 @@
         <v>0.375</v>
       </c>
       <c r="E2" s="75" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2" s="75">
         <v>0</v>
@@ -1116,10 +1052,10 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="88" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="77">
         <v>45824</v>
@@ -1128,7 +1064,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="E3" s="75" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3" s="75">
         <v>0</v>
@@ -1136,7 +1072,7 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="75" t="s">
         <v>0</v>
@@ -1148,7 +1084,7 @@
         <v>0.375</v>
       </c>
       <c r="E4" s="75" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F4" s="75">
         <v>0</v>
@@ -1156,7 +1092,7 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="88" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B5" s="75" t="s">
         <v>6</v>
@@ -1168,7 +1104,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F5" s="75">
         <v>0</v>
@@ -1176,7 +1112,7 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="88" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B6" s="75" t="s">
         <v>0</v>
@@ -1188,7 +1124,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E6" s="75" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F6" s="75">
         <v>0</v>
@@ -1196,7 +1132,7 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="75" t="s">
         <v>0</v>
@@ -1208,7 +1144,7 @@
         <v>0.375</v>
       </c>
       <c r="E7" s="75" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F7" s="75">
         <v>0</v>
@@ -1216,7 +1152,7 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="88" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B8" s="75" t="s">
         <v>6</v>
@@ -1228,7 +1164,7 @@
         <v>0.75</v>
       </c>
       <c r="E8" s="75" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F8" s="75">
         <v>0</v>
@@ -1236,10 +1172,10 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="88" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="77">
         <v>45828</v>
@@ -1248,7 +1184,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E9" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F9" s="75">
         <v>0</v>
@@ -1256,10 +1192,10 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="88" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="77">
         <v>45828</v>
@@ -1268,7 +1204,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E10" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F10" s="75">
         <v>23</v>
@@ -1276,10 +1212,10 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="88" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B11" s="75" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C11" s="77">
         <v>45825</v>
@@ -1288,7 +1224,7 @@
         <v>0.75</v>
       </c>
       <c r="E11" s="75" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F11" s="75">
         <v>0</v>
@@ -1296,10 +1232,10 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="88" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C12" s="77">
         <v>45832</v>
@@ -1308,7 +1244,7 @@
         <v>0.75</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F12" s="75">
         <v>0</v>
@@ -1316,10 +1252,10 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="88" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C13" s="77">
         <v>45839</v>
@@ -1328,7 +1264,7 @@
         <v>0.75</v>
       </c>
       <c r="E13" s="75" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F13" s="75">
         <v>0</v>
@@ -1336,7 +1272,7 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="88" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B14" s="75" t="s">
         <v>6</v>
@@ -1348,7 +1284,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E14" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F14" s="13">
         <v>28</v>
@@ -1356,7 +1292,7 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="88" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B15" s="75" t="s">
         <v>6</v>
@@ -1368,7 +1304,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="E15" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F15" s="8">
         <v>37</v>
@@ -1376,7 +1312,7 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="88" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B16" s="75" t="s">
         <v>7</v>
@@ -1388,7 +1324,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E16" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F16" s="13">
         <v>15</v>
@@ -1396,7 +1332,7 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="88" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B17" s="75" t="s">
         <v>7</v>
@@ -1408,7 +1344,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="E17" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F17" s="8">
         <v>15</v>
@@ -1416,7 +1352,7 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="88" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B18" s="75" t="s">
         <v>7</v>
@@ -1428,7 +1364,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E18" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F18" s="13">
         <v>15</v>
@@ -1436,7 +1372,7 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="88" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B19" s="75" t="s">
         <v>6</v>
@@ -1448,7 +1384,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E19" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F19" s="8">
         <v>30</v>
@@ -1456,7 +1392,7 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="88" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B20" s="75" t="s">
         <v>6</v>
@@ -1468,7 +1404,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="E20" s="75" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F20" s="13">
         <v>25</v>
@@ -1476,7 +1412,7 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="88" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B21" s="75" t="s">
         <v>0</v>
@@ -1488,7 +1424,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E21" s="75" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F21" s="75">
         <v>0</v>
@@ -1496,7 +1432,7 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>0</v>
@@ -1508,7 +1444,7 @@
         <v>0.375</v>
       </c>
       <c r="E22" s="75" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F22" s="75">
         <v>0</v>
@@ -1516,7 +1452,7 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="88" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B23" s="75" t="s">
         <v>0</v>
@@ -1528,7 +1464,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E23" s="75" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F23" s="75">
         <v>0</v>
@@ -9198,171 +9134,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="1" max="6" width="22.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="69"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A3" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="30"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="69"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A5" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="30"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="69"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="30"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="69"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="30"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="69"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="69"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="30"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="69"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A15" s="70"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="74"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/athens_events.xlsx
+++ b/athens_events.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sam/Desktop/athens-events-chatbot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6E6DD7-0745-154D-B3CD-AEA0E43ED708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3A92C4-4FDF-C649-B51D-309885B44531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="37">
   <si>
     <t>Event</t>
   </si>
@@ -46,19 +46,13 @@
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Comedy</t>
-  </si>
-  <si>
-    <t>Classes</t>
-  </si>
-  <si>
     <t>Marigold Farmers Market</t>
   </si>
   <si>
-    <t>Winterville Cultural Center</t>
+    <t>Marigold Auditorium</t>
   </si>
   <si>
-    <t>Marigold Auditorium</t>
+    <t>Health</t>
   </si>
   <si>
     <t>Pittard Park</t>
@@ -67,31 +61,10 @@
     <t>City Council Workshop</t>
   </si>
   <si>
-    <t>Summer Art Camp (3rd–5th grade)</t>
-  </si>
-  <si>
-    <t>Summer Art Camp (6th–8th grade)</t>
-  </si>
-  <si>
-    <t>Jim Cook</t>
-  </si>
-  <si>
-    <t>Concert, Front Porch Bookstore</t>
-  </si>
-  <si>
     <t>Marigold Monday Market</t>
   </si>
   <si>
     <t>Bank Building</t>
-  </si>
-  <si>
-    <t>Tracey and Jeff</t>
-  </si>
-  <si>
-    <t>Take This Comedy Presents: Little Women</t>
-  </si>
-  <si>
-    <t>The World’s Only Biker Comedy Hypnotist</t>
   </si>
   <si>
     <t>Historic Preservation Commission</t>
@@ -120,17 +93,57 @@
   <si>
     <t>The Return of FREEBIRD!</t>
   </si>
+  <si>
+    <t>Planning &amp; Zoning Commission Monthly Meeting</t>
+  </si>
+  <si>
+    <t>City Council Meeting</t>
+  </si>
+  <si>
+    <t>Downtown Development Authority Monthly Meeting</t>
+  </si>
+  <si>
+    <t>Friends of the Winterville Firefly Trail</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Not specified</t>
+  </si>
+  <si>
+    <t>Winterville Municipal Court</t>
+  </si>
+  <si>
+    <t>Arts</t>
+  </si>
+  <si>
+    <t>American Red Cross Blood Drive</t>
+  </si>
+  <si>
+    <t>101 Marigold Ln</t>
+  </si>
+  <si>
+    <t>Markets</t>
+  </si>
+  <si>
+    <t>Third Thursday Happy Hour</t>
+  </si>
+  <si>
+    <t>100 N Church St</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -219,6 +232,14 @@
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -470,7 +491,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -708,6 +729,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -787,7 +822,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F1002">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F1000">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F1000">
+    <sortCondition ref="C12:C1000"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Event"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category"/>
@@ -1001,7 +1039,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F1002"/>
+  <dimension ref="A1:F1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="51.33203125" customWidth="1"/>
@@ -1032,122 +1070,122 @@
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C2" s="77">
-        <v>45824</v>
+        <v>45838</v>
       </c>
       <c r="D2" s="78">
-        <v>0.375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="E2" s="75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="75">
+        <v>14</v>
+      </c>
+      <c r="F2" s="94">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="75" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="77">
-        <v>45824</v>
+        <v>45839</v>
       </c>
       <c r="D3" s="78">
-        <v>0.54166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="E3" s="75" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="75">
+        <v>17</v>
+      </c>
+      <c r="F3" s="93">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="77">
-        <v>45829</v>
+      <c r="C4" s="91">
+        <v>45843</v>
       </c>
       <c r="D4" s="78">
         <v>0.375</v>
       </c>
       <c r="E4" s="75" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="75">
+        <v>11</v>
+      </c>
+      <c r="F4" s="94">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="88" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="75" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="77">
-        <v>45829</v>
+        <v>45857</v>
       </c>
       <c r="D5" s="78">
-        <v>0.75</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="75">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F5" s="8">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6" s="77">
-        <v>45831</v>
+        <v>45876</v>
       </c>
       <c r="D6" s="78">
-        <v>0.41666666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="E6" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="75">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F6" s="13">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="88" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7" s="77">
-        <v>45836</v>
+        <v>45884</v>
       </c>
       <c r="D7" s="78">
-        <v>0.375</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E7" s="75" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="75">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F7" s="8">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
@@ -1155,96 +1193,96 @@
         <v>21</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="77">
-        <v>45836</v>
+        <v>45885</v>
       </c>
       <c r="D8" s="78">
-        <v>0.75</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E8" s="75" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="75">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F8" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="77">
-        <v>45828</v>
+        <v>45885</v>
       </c>
       <c r="D9" s="78">
         <v>0.79166666666666663</v>
       </c>
       <c r="E9" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="75">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F9" s="89">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="77">
-        <v>45828</v>
+        <v>22</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="92">
+        <v>45892</v>
       </c>
       <c r="D10" s="78">
         <v>0.79166666666666663</v>
       </c>
       <c r="E10" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="75">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="F10" s="89">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="88" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="77">
+        <v>45905</v>
+      </c>
+      <c r="D11" s="78">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E11" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="89">
         <v>25</v>
-      </c>
-      <c r="C11" s="77">
-        <v>45825</v>
-      </c>
-      <c r="D11" s="78">
-        <v>0.75</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="75">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="88" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C12" s="77">
-        <v>45832</v>
-      </c>
-      <c r="D12" s="78">
-        <v>0.75</v>
+        <v>45845</v>
+      </c>
+      <c r="D12" s="95">
+        <v>0.70833333333333337</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F12" s="75">
         <v>0</v>
@@ -1252,19 +1290,19 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="88" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C13" s="77">
-        <v>45839</v>
-      </c>
-      <c r="D13" s="78">
+        <v>45846</v>
+      </c>
+      <c r="D13" s="95">
         <v>0.75</v>
       </c>
       <c r="E13" s="75" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F13" s="75">
         <v>0</v>
@@ -1272,42 +1310,42 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="88" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" s="75" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C14" s="77">
-        <v>45857</v>
-      </c>
-      <c r="D14" s="78">
-        <v>0.83333333333333337</v>
+        <v>45847</v>
+      </c>
+      <c r="D14" s="95">
+        <v>0.75</v>
       </c>
       <c r="E14" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="13">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="F14" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="75" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C15" s="77">
-        <v>45876</v>
-      </c>
-      <c r="D15" s="78">
-        <v>0.83333333333333337</v>
+        <v>45847</v>
+      </c>
+      <c r="D15" s="95">
+        <v>0.79166666666666663</v>
       </c>
       <c r="E15" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="8">
-        <v>37</v>
+        <v>17</v>
+      </c>
+      <c r="F15" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
@@ -1315,211 +1353,271 @@
         <v>30</v>
       </c>
       <c r="B16" s="75" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C16" s="77">
-        <v>45884</v>
-      </c>
-      <c r="D16" s="78">
-        <v>0.79166666666666663</v>
+        <v>45852</v>
+      </c>
+      <c r="D16" s="95">
+        <v>0.70833333333333337</v>
       </c>
       <c r="E16" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="13">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F16" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="88" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B17" s="75" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C17" s="77">
-        <v>45885</v>
-      </c>
-      <c r="D17" s="78">
-        <v>0.58333333333333337</v>
+        <v>45853</v>
+      </c>
+      <c r="D17" s="95">
+        <v>0.75</v>
       </c>
       <c r="E17" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="8">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F17" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="88" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B18" s="75" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C18" s="77">
-        <v>45885</v>
-      </c>
-      <c r="D18" s="78">
-        <v>0.79166666666666663</v>
+        <v>45860</v>
+      </c>
+      <c r="D18" s="95">
+        <v>0.75</v>
       </c>
       <c r="E18" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="13">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="F18" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="88" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" s="75" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="77">
-        <v>45892</v>
+        <v>45866</v>
       </c>
       <c r="D19" s="78">
-        <v>0.79166666666666663</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="E19" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="8">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="F19" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="77">
-        <v>45905</v>
-      </c>
-      <c r="D20" s="78">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="13">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="B20" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="97">
+        <v>45838</v>
+      </c>
+      <c r="D20" s="98">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E20" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="75">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="77">
-        <v>45824</v>
-      </c>
-      <c r="D21" s="78">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E21" s="75" t="s">
-        <v>20</v>
+      <c r="A21" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="97">
+        <v>45843</v>
+      </c>
+      <c r="D21" s="98">
+        <v>0.375</v>
+      </c>
+      <c r="E21" s="85" t="s">
+        <v>11</v>
       </c>
       <c r="F21" s="75">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="88" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="11">
-        <v>45843</v>
-      </c>
-      <c r="D22" s="78">
-        <v>0.375</v>
-      </c>
-      <c r="E22" s="75" t="s">
-        <v>13</v>
+      <c r="A22" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="97">
+        <v>45845</v>
+      </c>
+      <c r="D22" s="98">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E22" s="85" t="s">
+        <v>36</v>
       </c>
       <c r="F22" s="75">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="77">
-        <v>45838</v>
-      </c>
-      <c r="D23" s="78">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E23" s="75" t="s">
-        <v>20</v>
+      <c r="A23" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="97">
+        <v>45850</v>
+      </c>
+      <c r="D23" s="98">
+        <v>0.375</v>
+      </c>
+      <c r="E23" s="85" t="s">
+        <v>11</v>
       </c>
       <c r="F23" s="75">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="13"/>
+      <c r="A24" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="97">
+        <v>45852</v>
+      </c>
+      <c r="D24" s="98">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E24" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="75">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="8"/>
+      <c r="A25" s="96" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="97">
+        <v>45855</v>
+      </c>
+      <c r="D25" s="98">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="E25" s="85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="75">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="13"/>
+      <c r="A26" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="97">
+        <v>45857</v>
+      </c>
+      <c r="D26" s="98">
+        <v>0.375</v>
+      </c>
+      <c r="E26" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="75">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="18"/>
+      <c r="A27" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="97">
+        <v>45859</v>
+      </c>
+      <c r="D27" s="98">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="75">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="23"/>
+      <c r="A28" s="96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="97">
+        <v>45864</v>
+      </c>
+      <c r="D28" s="98">
+        <v>0.375</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="75">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="18"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
       <c r="D30" s="12"/>
@@ -1543,12 +1641,12 @@
       <c r="F32" s="13"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="25"/>
       <c r="C33" s="6"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="8"/>
+      <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1">
       <c r="A34" s="9"/>
@@ -1559,12 +1657,12 @@
       <c r="F34" s="13"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
       <c r="C35" s="6"/>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="18"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
       <c r="A36" s="9"/>
@@ -1623,12 +1721,12 @@
       <c r="F42" s="13"/>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A43" s="4"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="8"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="18"/>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1">
       <c r="A44" s="9"/>
@@ -1639,12 +1737,12 @@
       <c r="F44" s="13"/>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="18"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
@@ -1703,12 +1801,12 @@
       <c r="F52" s="13"/>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="8"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="18"/>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1">
       <c r="A54" s="9"/>
@@ -1719,12 +1817,12 @@
       <c r="F54" s="13"/>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A55" s="24"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="18"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="8"/>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1">
       <c r="A56" s="9"/>
@@ -1742,7 +1840,7 @@
       <c r="E57" s="5"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1">
+    <row r="58" spans="1:6" ht="13">
       <c r="A58" s="9"/>
       <c r="B58" s="10"/>
       <c r="C58" s="11"/>
@@ -1750,7 +1848,7 @@
       <c r="E58" s="10"/>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1">
+    <row r="59" spans="1:6" ht="13">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -1895,12 +1993,12 @@
       <c r="F76" s="13"/>
     </row>
     <row r="77" spans="1:6" ht="13">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
+      <c r="A77" s="24"/>
+      <c r="B77" s="25"/>
       <c r="C77" s="6"/>
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="8"/>
+      <c r="F77" s="18"/>
     </row>
     <row r="78" spans="1:6" ht="13">
       <c r="A78" s="9"/>
@@ -1911,12 +2009,12 @@
       <c r="F78" s="13"/>
     </row>
     <row r="79" spans="1:6" ht="13">
-      <c r="A79" s="24"/>
-      <c r="B79" s="25"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="5"/>
       <c r="C79" s="6"/>
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="18"/>
+      <c r="F79" s="8"/>
     </row>
     <row r="80" spans="1:6" ht="13">
       <c r="A80" s="9"/>
@@ -2103,12 +2201,12 @@
       <c r="F102" s="13"/>
     </row>
     <row r="103" spans="1:6" ht="13">
-      <c r="A103" s="4"/>
-      <c r="B103" s="5"/>
+      <c r="A103" s="24"/>
+      <c r="B103" s="25"/>
       <c r="C103" s="6"/>
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
-      <c r="F103" s="8"/>
+      <c r="F103" s="18"/>
     </row>
     <row r="104" spans="1:6" ht="13">
       <c r="A104" s="9"/>
@@ -2119,12 +2217,12 @@
       <c r="F104" s="13"/>
     </row>
     <row r="105" spans="1:6" ht="13">
-      <c r="A105" s="24"/>
-      <c r="B105" s="25"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="5"/>
       <c r="C105" s="6"/>
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
-      <c r="F105" s="18"/>
+      <c r="F105" s="8"/>
     </row>
     <row r="106" spans="1:6" ht="13">
       <c r="A106" s="9"/>
@@ -2159,12 +2257,12 @@
       <c r="F109" s="8"/>
     </row>
     <row r="110" spans="1:6" ht="13">
-      <c r="A110" s="9"/>
-      <c r="B110" s="10"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="12"/>
-      <c r="E110" s="10"/>
-      <c r="F110" s="13"/>
+      <c r="A110" s="19"/>
+      <c r="B110" s="20"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="20"/>
+      <c r="F110" s="23"/>
     </row>
     <row r="111" spans="1:6" ht="13">
       <c r="A111" s="4"/>
@@ -2175,11 +2273,11 @@
       <c r="F111" s="8"/>
     </row>
     <row r="112" spans="1:6" ht="13">
-      <c r="A112" s="19"/>
-      <c r="B112" s="20"/>
-      <c r="C112" s="21"/>
-      <c r="D112" s="22"/>
-      <c r="E112" s="20"/>
+      <c r="A112" s="28"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="10"/>
       <c r="F112" s="23"/>
     </row>
     <row r="113" spans="1:6" ht="13">
@@ -2191,12 +2289,12 @@
       <c r="F113" s="8"/>
     </row>
     <row r="114" spans="1:6" ht="13">
-      <c r="A114" s="28"/>
-      <c r="B114" s="29"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="10"/>
       <c r="C114" s="11"/>
       <c r="D114" s="12"/>
       <c r="E114" s="10"/>
-      <c r="F114" s="23"/>
+      <c r="F114" s="13"/>
     </row>
     <row r="115" spans="1:6" ht="13">
       <c r="A115" s="4"/>
@@ -2223,12 +2321,12 @@
       <c r="F117" s="8"/>
     </row>
     <row r="118" spans="1:6" ht="13">
-      <c r="A118" s="9"/>
+      <c r="A118" s="19"/>
       <c r="B118" s="10"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="12"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="22"/>
       <c r="E118" s="10"/>
-      <c r="F118" s="13"/>
+      <c r="F118" s="30"/>
     </row>
     <row r="119" spans="1:6" ht="13">
       <c r="A119" s="4"/>
@@ -2238,32 +2336,32 @@
       <c r="E119" s="5"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120" spans="1:6" ht="13">
-      <c r="A120" s="19"/>
+    <row r="120" spans="1:6" ht="16">
+      <c r="A120" s="31"/>
       <c r="B120" s="10"/>
       <c r="C120" s="21"/>
       <c r="D120" s="22"/>
-      <c r="E120" s="10"/>
-      <c r="F120" s="30"/>
-    </row>
-    <row r="121" spans="1:6" ht="13">
-      <c r="A121" s="4"/>
+      <c r="E120" s="32"/>
+      <c r="F120" s="23"/>
+    </row>
+    <row r="121" spans="1:6" ht="16">
+      <c r="A121" s="33"/>
       <c r="B121" s="5"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="8"/>
+      <c r="C121" s="16"/>
+      <c r="D121" s="17"/>
+      <c r="E121" s="32"/>
+      <c r="F121" s="18"/>
     </row>
     <row r="122" spans="1:6" ht="16">
       <c r="A122" s="31"/>
       <c r="B122" s="10"/>
       <c r="C122" s="21"/>
-      <c r="D122" s="22"/>
+      <c r="D122" s="34"/>
       <c r="E122" s="32"/>
       <c r="F122" s="23"/>
     </row>
     <row r="123" spans="1:6" ht="16">
-      <c r="A123" s="33"/>
+      <c r="A123" s="31"/>
       <c r="B123" s="5"/>
       <c r="C123" s="16"/>
       <c r="D123" s="17"/>
@@ -2274,25 +2372,25 @@
       <c r="A124" s="31"/>
       <c r="B124" s="10"/>
       <c r="C124" s="21"/>
-      <c r="D124" s="34"/>
+      <c r="D124" s="22"/>
       <c r="E124" s="32"/>
       <c r="F124" s="23"/>
     </row>
-    <row r="125" spans="1:6" ht="16">
-      <c r="A125" s="31"/>
+    <row r="125" spans="1:6" ht="13">
+      <c r="A125" s="4"/>
       <c r="B125" s="5"/>
-      <c r="C125" s="16"/>
-      <c r="D125" s="17"/>
-      <c r="E125" s="32"/>
-      <c r="F125" s="18"/>
-    </row>
-    <row r="126" spans="1:6" ht="16">
-      <c r="A126" s="31"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="8"/>
+    </row>
+    <row r="126" spans="1:6" ht="13">
+      <c r="A126" s="9"/>
       <c r="B126" s="10"/>
-      <c r="C126" s="21"/>
-      <c r="D126" s="22"/>
-      <c r="E126" s="32"/>
-      <c r="F126" s="23"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="10"/>
+      <c r="F126" s="13"/>
     </row>
     <row r="127" spans="1:6" ht="13">
       <c r="A127" s="4"/>
@@ -2343,20 +2441,20 @@
       <c r="F132" s="13"/>
     </row>
     <row r="133" spans="1:6" ht="13">
-      <c r="A133" s="4"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="8"/>
+      <c r="A133" s="35"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="37"/>
+      <c r="D133" s="38"/>
+      <c r="E133" s="36"/>
+      <c r="F133" s="39"/>
     </row>
     <row r="134" spans="1:6" ht="13">
-      <c r="A134" s="9"/>
-      <c r="B134" s="10"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="12"/>
-      <c r="E134" s="10"/>
-      <c r="F134" s="13"/>
+      <c r="A134" s="40"/>
+      <c r="B134" s="41"/>
+      <c r="C134" s="42"/>
+      <c r="D134" s="43"/>
+      <c r="E134" s="41"/>
+      <c r="F134" s="44"/>
     </row>
     <row r="135" spans="1:6" ht="13">
       <c r="A135" s="35"/>
@@ -2375,27 +2473,27 @@
       <c r="F136" s="44"/>
     </row>
     <row r="137" spans="1:6" ht="13">
-      <c r="A137" s="35"/>
-      <c r="B137" s="36"/>
-      <c r="C137" s="37"/>
-      <c r="D137" s="38"/>
-      <c r="E137" s="36"/>
-      <c r="F137" s="39"/>
-    </row>
-    <row r="138" spans="1:6" ht="13">
-      <c r="A138" s="40"/>
+      <c r="A137" s="45"/>
+      <c r="B137" s="46"/>
+      <c r="C137" s="47"/>
+      <c r="D137" s="48"/>
+      <c r="E137" s="46"/>
+      <c r="F137" s="49"/>
+    </row>
+    <row r="138" spans="1:6" ht="16">
+      <c r="A138" s="31"/>
       <c r="B138" s="41"/>
-      <c r="C138" s="42"/>
-      <c r="D138" s="43"/>
-      <c r="E138" s="41"/>
-      <c r="F138" s="44"/>
+      <c r="C138" s="50"/>
+      <c r="D138" s="51"/>
+      <c r="E138" s="52"/>
+      <c r="F138" s="53"/>
     </row>
     <row r="139" spans="1:6" ht="13">
-      <c r="A139" s="45"/>
-      <c r="B139" s="46"/>
+      <c r="A139" s="54"/>
+      <c r="B139" s="36"/>
       <c r="C139" s="47"/>
       <c r="D139" s="48"/>
-      <c r="E139" s="46"/>
+      <c r="E139" s="55"/>
       <c r="F139" s="49"/>
     </row>
     <row r="140" spans="1:6" ht="16">
@@ -2406,12 +2504,12 @@
       <c r="E140" s="52"/>
       <c r="F140" s="53"/>
     </row>
-    <row r="141" spans="1:6" ht="13">
-      <c r="A141" s="54"/>
-      <c r="B141" s="36"/>
+    <row r="141" spans="1:6" ht="16">
+      <c r="A141" s="31"/>
+      <c r="B141" s="46"/>
       <c r="C141" s="47"/>
       <c r="D141" s="48"/>
-      <c r="E141" s="55"/>
+      <c r="E141" s="52"/>
       <c r="F141" s="49"/>
     </row>
     <row r="142" spans="1:6" ht="16">
@@ -2424,7 +2522,7 @@
     </row>
     <row r="143" spans="1:6" ht="16">
       <c r="A143" s="31"/>
-      <c r="B143" s="46"/>
+      <c r="B143" s="56"/>
       <c r="C143" s="47"/>
       <c r="D143" s="48"/>
       <c r="E143" s="52"/>
@@ -2432,59 +2530,59 @@
     </row>
     <row r="144" spans="1:6" ht="16">
       <c r="A144" s="31"/>
-      <c r="B144" s="41"/>
+      <c r="B144" s="57"/>
       <c r="C144" s="50"/>
       <c r="D144" s="51"/>
       <c r="E144" s="52"/>
       <c r="F144" s="53"/>
     </row>
-    <row r="145" spans="1:6" ht="16">
-      <c r="A145" s="31"/>
-      <c r="B145" s="56"/>
+    <row r="145" spans="1:6" ht="13">
+      <c r="A145" s="54"/>
+      <c r="B145" s="46"/>
       <c r="C145" s="47"/>
       <c r="D145" s="48"/>
-      <c r="E145" s="52"/>
+      <c r="E145" s="46"/>
       <c r="F145" s="49"/>
     </row>
     <row r="146" spans="1:6" ht="16">
       <c r="A146" s="31"/>
-      <c r="B146" s="57"/>
+      <c r="B146" s="41"/>
       <c r="C146" s="50"/>
       <c r="D146" s="51"/>
       <c r="E146" s="52"/>
       <c r="F146" s="53"/>
     </row>
-    <row r="147" spans="1:6" ht="13">
-      <c r="A147" s="54"/>
-      <c r="B147" s="46"/>
+    <row r="147" spans="1:6" ht="16">
+      <c r="A147" s="31"/>
+      <c r="B147" s="36"/>
       <c r="C147" s="47"/>
       <c r="D147" s="48"/>
-      <c r="E147" s="46"/>
+      <c r="E147" s="52"/>
       <c r="F147" s="49"/>
     </row>
     <row r="148" spans="1:6" ht="16">
-      <c r="A148" s="31"/>
-      <c r="B148" s="41"/>
+      <c r="A148" s="58"/>
+      <c r="B148" s="59"/>
       <c r="C148" s="50"/>
       <c r="D148" s="51"/>
       <c r="E148" s="52"/>
-      <c r="F148" s="53"/>
-    </row>
-    <row r="149" spans="1:6" ht="16">
-      <c r="A149" s="31"/>
+      <c r="F148" s="60"/>
+    </row>
+    <row r="149" spans="1:6" ht="13">
+      <c r="A149" s="35"/>
       <c r="B149" s="36"/>
-      <c r="C149" s="47"/>
-      <c r="D149" s="48"/>
-      <c r="E149" s="52"/>
-      <c r="F149" s="49"/>
-    </row>
-    <row r="150" spans="1:6" ht="16">
-      <c r="A150" s="58"/>
-      <c r="B150" s="59"/>
-      <c r="C150" s="50"/>
-      <c r="D150" s="51"/>
-      <c r="E150" s="52"/>
-      <c r="F150" s="60"/>
+      <c r="C149" s="37"/>
+      <c r="D149" s="38"/>
+      <c r="E149" s="36"/>
+      <c r="F149" s="39"/>
+    </row>
+    <row r="150" spans="1:6" ht="13">
+      <c r="A150" s="40"/>
+      <c r="B150" s="41"/>
+      <c r="C150" s="42"/>
+      <c r="D150" s="43"/>
+      <c r="E150" s="41"/>
+      <c r="F150" s="44"/>
     </row>
     <row r="151" spans="1:6" ht="13">
       <c r="A151" s="35"/>
@@ -2543,12 +2641,12 @@
       <c r="F157" s="39"/>
     </row>
     <row r="158" spans="1:6" ht="13">
-      <c r="A158" s="40"/>
-      <c r="B158" s="41"/>
+      <c r="A158" s="61"/>
+      <c r="B158" s="57"/>
       <c r="C158" s="42"/>
       <c r="D158" s="43"/>
       <c r="E158" s="41"/>
-      <c r="F158" s="44"/>
+      <c r="F158" s="53"/>
     </row>
     <row r="159" spans="1:6" ht="13">
       <c r="A159" s="35"/>
@@ -2559,12 +2657,12 @@
       <c r="F159" s="39"/>
     </row>
     <row r="160" spans="1:6" ht="13">
-      <c r="A160" s="61"/>
-      <c r="B160" s="57"/>
+      <c r="A160" s="40"/>
+      <c r="B160" s="41"/>
       <c r="C160" s="42"/>
       <c r="D160" s="43"/>
       <c r="E160" s="41"/>
-      <c r="F160" s="53"/>
+      <c r="F160" s="44"/>
     </row>
     <row r="161" spans="1:6" ht="13">
       <c r="A161" s="35"/>
@@ -2607,52 +2705,52 @@
       <c r="F165" s="39"/>
     </row>
     <row r="166" spans="1:6" ht="13">
-      <c r="A166" s="40"/>
-      <c r="B166" s="41"/>
-      <c r="C166" s="42"/>
-      <c r="D166" s="43"/>
-      <c r="E166" s="41"/>
-      <c r="F166" s="44"/>
+      <c r="A166" s="62"/>
+      <c r="B166" s="59"/>
+      <c r="C166" s="50"/>
+      <c r="D166" s="51"/>
+      <c r="E166" s="59"/>
+      <c r="F166" s="53"/>
     </row>
     <row r="167" spans="1:6" ht="13">
-      <c r="A167" s="35"/>
-      <c r="B167" s="36"/>
-      <c r="C167" s="37"/>
-      <c r="D167" s="38"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="39"/>
+      <c r="A167" s="45"/>
+      <c r="B167" s="46"/>
+      <c r="C167" s="47"/>
+      <c r="D167" s="48"/>
+      <c r="E167" s="55"/>
+      <c r="F167" s="49"/>
     </row>
     <row r="168" spans="1:6" ht="13">
-      <c r="A168" s="62"/>
+      <c r="A168" s="31"/>
       <c r="B168" s="59"/>
       <c r="C168" s="50"/>
       <c r="D168" s="51"/>
-      <c r="E168" s="59"/>
+      <c r="E168" s="55"/>
       <c r="F168" s="53"/>
     </row>
     <row r="169" spans="1:6" ht="13">
-      <c r="A169" s="45"/>
-      <c r="B169" s="46"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="56"/>
       <c r="C169" s="47"/>
       <c r="D169" s="48"/>
       <c r="E169" s="55"/>
       <c r="F169" s="49"/>
     </row>
     <row r="170" spans="1:6" ht="13">
-      <c r="A170" s="31"/>
-      <c r="B170" s="59"/>
-      <c r="C170" s="50"/>
-      <c r="D170" s="51"/>
-      <c r="E170" s="55"/>
-      <c r="F170" s="53"/>
+      <c r="A170" s="40"/>
+      <c r="B170" s="41"/>
+      <c r="C170" s="42"/>
+      <c r="D170" s="43"/>
+      <c r="E170" s="41"/>
+      <c r="F170" s="44"/>
     </row>
     <row r="171" spans="1:6" ht="13">
-      <c r="A171" s="31"/>
-      <c r="B171" s="56"/>
-      <c r="C171" s="47"/>
-      <c r="D171" s="48"/>
-      <c r="E171" s="55"/>
-      <c r="F171" s="49"/>
+      <c r="A171" s="35"/>
+      <c r="B171" s="36"/>
+      <c r="C171" s="37"/>
+      <c r="D171" s="38"/>
+      <c r="E171" s="36"/>
+      <c r="F171" s="39"/>
     </row>
     <row r="172" spans="1:6" ht="13">
       <c r="A172" s="40"/>
@@ -2695,27 +2793,27 @@
       <c r="F176" s="44"/>
     </row>
     <row r="177" spans="1:6" ht="13">
-      <c r="A177" s="35"/>
-      <c r="B177" s="36"/>
-      <c r="C177" s="37"/>
-      <c r="D177" s="38"/>
-      <c r="E177" s="36"/>
-      <c r="F177" s="39"/>
+      <c r="A177" s="63"/>
+      <c r="B177" s="56"/>
+      <c r="C177" s="64"/>
+      <c r="D177" s="65"/>
+      <c r="E177" s="56"/>
+      <c r="F177" s="49"/>
     </row>
     <row r="178" spans="1:6" ht="13">
-      <c r="A178" s="40"/>
+      <c r="A178" s="62"/>
       <c r="B178" s="41"/>
-      <c r="C178" s="42"/>
-      <c r="D178" s="43"/>
-      <c r="E178" s="41"/>
-      <c r="F178" s="44"/>
+      <c r="C178" s="50"/>
+      <c r="D178" s="51"/>
+      <c r="E178" s="59"/>
+      <c r="F178" s="53"/>
     </row>
     <row r="179" spans="1:6" ht="13">
-      <c r="A179" s="63"/>
-      <c r="B179" s="56"/>
-      <c r="C179" s="64"/>
-      <c r="D179" s="65"/>
-      <c r="E179" s="56"/>
+      <c r="A179" s="45"/>
+      <c r="B179" s="36"/>
+      <c r="C179" s="47"/>
+      <c r="D179" s="48"/>
+      <c r="E179" s="46"/>
       <c r="F179" s="49"/>
     </row>
     <row r="180" spans="1:6" ht="13">
@@ -2728,39 +2826,39 @@
     </row>
     <row r="181" spans="1:6" ht="13">
       <c r="A181" s="45"/>
-      <c r="B181" s="36"/>
+      <c r="B181" s="56"/>
       <c r="C181" s="47"/>
       <c r="D181" s="48"/>
       <c r="E181" s="46"/>
       <c r="F181" s="49"/>
     </row>
     <row r="182" spans="1:6" ht="13">
-      <c r="A182" s="62"/>
-      <c r="B182" s="41"/>
-      <c r="C182" s="50"/>
-      <c r="D182" s="51"/>
-      <c r="E182" s="59"/>
+      <c r="A182" s="61"/>
+      <c r="B182" s="57"/>
+      <c r="C182" s="42"/>
+      <c r="D182" s="43"/>
+      <c r="E182" s="41"/>
       <c r="F182" s="53"/>
     </row>
     <row r="183" spans="1:6" ht="13">
       <c r="A183" s="45"/>
-      <c r="B183" s="56"/>
+      <c r="B183" s="46"/>
       <c r="C183" s="47"/>
       <c r="D183" s="48"/>
       <c r="E183" s="46"/>
       <c r="F183" s="49"/>
     </row>
     <row r="184" spans="1:6" ht="13">
-      <c r="A184" s="61"/>
-      <c r="B184" s="57"/>
-      <c r="C184" s="42"/>
-      <c r="D184" s="43"/>
-      <c r="E184" s="41"/>
+      <c r="A184" s="62"/>
+      <c r="B184" s="41"/>
+      <c r="C184" s="50"/>
+      <c r="D184" s="51"/>
+      <c r="E184" s="59"/>
       <c r="F184" s="53"/>
     </row>
     <row r="185" spans="1:6" ht="13">
       <c r="A185" s="45"/>
-      <c r="B185" s="46"/>
+      <c r="B185" s="56"/>
       <c r="C185" s="47"/>
       <c r="D185" s="48"/>
       <c r="E185" s="46"/>
@@ -2776,7 +2874,7 @@
     </row>
     <row r="187" spans="1:6" ht="13">
       <c r="A187" s="45"/>
-      <c r="B187" s="56"/>
+      <c r="B187" s="36"/>
       <c r="C187" s="47"/>
       <c r="D187" s="48"/>
       <c r="E187" s="46"/>
@@ -2800,34 +2898,34 @@
     </row>
     <row r="190" spans="1:6" ht="13">
       <c r="A190" s="62"/>
-      <c r="B190" s="41"/>
+      <c r="B190" s="59"/>
       <c r="C190" s="50"/>
       <c r="D190" s="51"/>
       <c r="E190" s="59"/>
       <c r="F190" s="53"/>
     </row>
     <row r="191" spans="1:6" ht="13">
-      <c r="A191" s="45"/>
-      <c r="B191" s="36"/>
-      <c r="C191" s="47"/>
-      <c r="D191" s="48"/>
-      <c r="E191" s="46"/>
+      <c r="A191" s="63"/>
+      <c r="B191" s="56"/>
+      <c r="C191" s="37"/>
+      <c r="D191" s="38"/>
+      <c r="E191" s="36"/>
       <c r="F191" s="49"/>
     </row>
     <row r="192" spans="1:6" ht="13">
       <c r="A192" s="62"/>
-      <c r="B192" s="59"/>
+      <c r="B192" s="41"/>
       <c r="C192" s="50"/>
       <c r="D192" s="51"/>
-      <c r="E192" s="59"/>
-      <c r="F192" s="53"/>
+      <c r="E192" s="41"/>
+      <c r="F192" s="60"/>
     </row>
     <row r="193" spans="1:6" ht="13">
-      <c r="A193" s="63"/>
-      <c r="B193" s="56"/>
-      <c r="C193" s="37"/>
-      <c r="D193" s="38"/>
-      <c r="E193" s="36"/>
+      <c r="A193" s="45"/>
+      <c r="B193" s="46"/>
+      <c r="C193" s="47"/>
+      <c r="D193" s="48"/>
+      <c r="E193" s="46"/>
       <c r="F193" s="49"/>
     </row>
     <row r="194" spans="1:6" ht="13">
@@ -2835,12 +2933,12 @@
       <c r="B194" s="41"/>
       <c r="C194" s="50"/>
       <c r="D194" s="51"/>
-      <c r="E194" s="41"/>
-      <c r="F194" s="60"/>
+      <c r="E194" s="59"/>
+      <c r="F194" s="49"/>
     </row>
     <row r="195" spans="1:6" ht="13">
       <c r="A195" s="45"/>
-      <c r="B195" s="46"/>
+      <c r="B195" s="36"/>
       <c r="C195" s="47"/>
       <c r="D195" s="48"/>
       <c r="E195" s="46"/>
@@ -2887,11 +2985,11 @@
       <c r="F200" s="49"/>
     </row>
     <row r="201" spans="1:6" ht="13">
-      <c r="A201" s="45"/>
-      <c r="B201" s="36"/>
-      <c r="C201" s="47"/>
-      <c r="D201" s="48"/>
-      <c r="E201" s="46"/>
+      <c r="A201" s="63"/>
+      <c r="B201" s="56"/>
+      <c r="C201" s="37"/>
+      <c r="D201" s="38"/>
+      <c r="E201" s="36"/>
       <c r="F201" s="49"/>
     </row>
     <row r="202" spans="1:6" ht="13">
@@ -2899,24 +2997,24 @@
       <c r="B202" s="41"/>
       <c r="C202" s="50"/>
       <c r="D202" s="51"/>
-      <c r="E202" s="59"/>
-      <c r="F202" s="49"/>
+      <c r="E202" s="41"/>
+      <c r="F202" s="60"/>
     </row>
     <row r="203" spans="1:6" ht="13">
-      <c r="A203" s="63"/>
-      <c r="B203" s="56"/>
-      <c r="C203" s="37"/>
-      <c r="D203" s="38"/>
-      <c r="E203" s="36"/>
+      <c r="A203" s="45"/>
+      <c r="B203" s="46"/>
+      <c r="C203" s="47"/>
+      <c r="D203" s="48"/>
+      <c r="E203" s="46"/>
       <c r="F203" s="49"/>
     </row>
     <row r="204" spans="1:6" ht="13">
       <c r="A204" s="62"/>
-      <c r="B204" s="41"/>
+      <c r="B204" s="59"/>
       <c r="C204" s="50"/>
       <c r="D204" s="51"/>
-      <c r="E204" s="41"/>
-      <c r="F204" s="60"/>
+      <c r="E204" s="59"/>
+      <c r="F204" s="53"/>
     </row>
     <row r="205" spans="1:6" ht="13">
       <c r="A205" s="45"/>
@@ -2927,11 +3025,11 @@
       <c r="F205" s="49"/>
     </row>
     <row r="206" spans="1:6" ht="13">
-      <c r="A206" s="62"/>
-      <c r="B206" s="59"/>
-      <c r="C206" s="50"/>
-      <c r="D206" s="51"/>
-      <c r="E206" s="59"/>
+      <c r="A206" s="61"/>
+      <c r="B206" s="57"/>
+      <c r="C206" s="42"/>
+      <c r="D206" s="43"/>
+      <c r="E206" s="41"/>
       <c r="F206" s="53"/>
     </row>
     <row r="207" spans="1:6" ht="13">
@@ -2945,49 +3043,49 @@
     <row r="208" spans="1:6" ht="13">
       <c r="A208" s="61"/>
       <c r="B208" s="57"/>
-      <c r="C208" s="42"/>
-      <c r="D208" s="43"/>
-      <c r="E208" s="41"/>
+      <c r="C208" s="67"/>
+      <c r="D208" s="68"/>
+      <c r="E208" s="57"/>
       <c r="F208" s="53"/>
     </row>
     <row r="209" spans="1:6" ht="13">
-      <c r="A209" s="45"/>
-      <c r="B209" s="46"/>
-      <c r="C209" s="47"/>
-      <c r="D209" s="48"/>
-      <c r="E209" s="46"/>
+      <c r="A209" s="63"/>
+      <c r="B209" s="56"/>
+      <c r="C209" s="37"/>
+      <c r="D209" s="38"/>
+      <c r="E209" s="36"/>
       <c r="F209" s="49"/>
     </row>
     <row r="210" spans="1:6" ht="13">
-      <c r="A210" s="61"/>
-      <c r="B210" s="57"/>
-      <c r="C210" s="67"/>
-      <c r="D210" s="68"/>
-      <c r="E210" s="57"/>
+      <c r="A210" s="62"/>
+      <c r="B210" s="59"/>
+      <c r="C210" s="50"/>
+      <c r="D210" s="51"/>
+      <c r="E210" s="59"/>
       <c r="F210" s="53"/>
     </row>
     <row r="211" spans="1:6" ht="13">
-      <c r="A211" s="63"/>
-      <c r="B211" s="56"/>
-      <c r="C211" s="37"/>
-      <c r="D211" s="38"/>
+      <c r="A211" s="45"/>
+      <c r="B211" s="36"/>
+      <c r="C211" s="47"/>
+      <c r="D211" s="48"/>
       <c r="E211" s="36"/>
       <c r="F211" s="49"/>
     </row>
     <row r="212" spans="1:6" ht="13">
-      <c r="A212" s="62"/>
-      <c r="B212" s="59"/>
-      <c r="C212" s="50"/>
-      <c r="D212" s="51"/>
-      <c r="E212" s="59"/>
+      <c r="A212" s="61"/>
+      <c r="B212" s="57"/>
+      <c r="C212" s="42"/>
+      <c r="D212" s="43"/>
+      <c r="E212" s="41"/>
       <c r="F212" s="53"/>
     </row>
     <row r="213" spans="1:6" ht="13">
       <c r="A213" s="45"/>
-      <c r="B213" s="36"/>
+      <c r="B213" s="46"/>
       <c r="C213" s="47"/>
       <c r="D213" s="48"/>
-      <c r="E213" s="36"/>
+      <c r="E213" s="46"/>
       <c r="F213" s="49"/>
     </row>
     <row r="214" spans="1:6" ht="13">
@@ -3000,42 +3098,42 @@
     </row>
     <row r="215" spans="1:6" ht="13">
       <c r="A215" s="45"/>
-      <c r="B215" s="46"/>
+      <c r="B215" s="36"/>
       <c r="C215" s="47"/>
       <c r="D215" s="48"/>
-      <c r="E215" s="46"/>
+      <c r="E215" s="36"/>
       <c r="F215" s="49"/>
     </row>
     <row r="216" spans="1:6" ht="13">
-      <c r="A216" s="61"/>
-      <c r="B216" s="57"/>
-      <c r="C216" s="42"/>
-      <c r="D216" s="43"/>
+      <c r="A216" s="62"/>
+      <c r="B216" s="41"/>
+      <c r="C216" s="50"/>
+      <c r="D216" s="51"/>
       <c r="E216" s="41"/>
-      <c r="F216" s="53"/>
+      <c r="F216" s="60"/>
     </row>
     <row r="217" spans="1:6" ht="13">
       <c r="A217" s="45"/>
-      <c r="B217" s="36"/>
+      <c r="B217" s="46"/>
       <c r="C217" s="47"/>
       <c r="D217" s="48"/>
-      <c r="E217" s="36"/>
+      <c r="E217" s="46"/>
       <c r="F217" s="49"/>
     </row>
     <row r="218" spans="1:6" ht="13">
       <c r="A218" s="62"/>
-      <c r="B218" s="41"/>
+      <c r="B218" s="59"/>
       <c r="C218" s="50"/>
       <c r="D218" s="51"/>
-      <c r="E218" s="41"/>
-      <c r="F218" s="60"/>
+      <c r="E218" s="59"/>
+      <c r="F218" s="53"/>
     </row>
     <row r="219" spans="1:6" ht="13">
-      <c r="A219" s="45"/>
-      <c r="B219" s="46"/>
-      <c r="C219" s="47"/>
-      <c r="D219" s="48"/>
-      <c r="E219" s="46"/>
+      <c r="A219" s="63"/>
+      <c r="B219" s="56"/>
+      <c r="C219" s="37"/>
+      <c r="D219" s="38"/>
+      <c r="E219" s="36"/>
       <c r="F219" s="49"/>
     </row>
     <row r="220" spans="1:6" ht="13">
@@ -3049,42 +3147,42 @@
     <row r="221" spans="1:6" ht="13">
       <c r="A221" s="63"/>
       <c r="B221" s="56"/>
-      <c r="C221" s="37"/>
-      <c r="D221" s="38"/>
-      <c r="E221" s="36"/>
+      <c r="C221" s="64"/>
+      <c r="D221" s="65"/>
+      <c r="E221" s="56"/>
       <c r="F221" s="49"/>
     </row>
     <row r="222" spans="1:6" ht="13">
-      <c r="A222" s="62"/>
-      <c r="B222" s="59"/>
-      <c r="C222" s="50"/>
-      <c r="D222" s="51"/>
-      <c r="E222" s="59"/>
+      <c r="A222" s="61"/>
+      <c r="B222" s="57"/>
+      <c r="C222" s="42"/>
+      <c r="D222" s="43"/>
+      <c r="E222" s="41"/>
       <c r="F222" s="53"/>
     </row>
     <row r="223" spans="1:6" ht="13">
-      <c r="A223" s="63"/>
-      <c r="B223" s="56"/>
-      <c r="C223" s="64"/>
-      <c r="D223" s="65"/>
-      <c r="E223" s="56"/>
-      <c r="F223" s="49"/>
+      <c r="A223" s="45"/>
+      <c r="B223" s="36"/>
+      <c r="C223" s="47"/>
+      <c r="D223" s="48"/>
+      <c r="E223" s="36"/>
+      <c r="F223" s="66"/>
     </row>
     <row r="224" spans="1:6" ht="13">
-      <c r="A224" s="61"/>
-      <c r="B224" s="57"/>
-      <c r="C224" s="42"/>
-      <c r="D224" s="43"/>
-      <c r="E224" s="41"/>
+      <c r="A224" s="62"/>
+      <c r="B224" s="59"/>
+      <c r="C224" s="50"/>
+      <c r="D224" s="51"/>
+      <c r="E224" s="59"/>
       <c r="F224" s="53"/>
     </row>
     <row r="225" spans="1:6" ht="13">
-      <c r="A225" s="45"/>
-      <c r="B225" s="36"/>
-      <c r="C225" s="47"/>
-      <c r="D225" s="48"/>
+      <c r="A225" s="63"/>
+      <c r="B225" s="56"/>
+      <c r="C225" s="37"/>
+      <c r="D225" s="38"/>
       <c r="E225" s="36"/>
-      <c r="F225" s="66"/>
+      <c r="F225" s="49"/>
     </row>
     <row r="226" spans="1:6" ht="13">
       <c r="A226" s="62"/>
@@ -3104,27 +3202,27 @@
     </row>
     <row r="228" spans="1:6" ht="13">
       <c r="A228" s="62"/>
-      <c r="B228" s="59"/>
+      <c r="B228" s="41"/>
       <c r="C228" s="50"/>
       <c r="D228" s="51"/>
-      <c r="E228" s="59"/>
-      <c r="F228" s="53"/>
+      <c r="E228" s="41"/>
+      <c r="F228" s="60"/>
     </row>
     <row r="229" spans="1:6" ht="13">
-      <c r="A229" s="63"/>
-      <c r="B229" s="56"/>
-      <c r="C229" s="37"/>
-      <c r="D229" s="38"/>
-      <c r="E229" s="36"/>
+      <c r="A229" s="45"/>
+      <c r="B229" s="46"/>
+      <c r="C229" s="47"/>
+      <c r="D229" s="48"/>
+      <c r="E229" s="46"/>
       <c r="F229" s="49"/>
     </row>
     <row r="230" spans="1:6" ht="13">
       <c r="A230" s="62"/>
-      <c r="B230" s="41"/>
+      <c r="B230" s="59"/>
       <c r="C230" s="50"/>
       <c r="D230" s="51"/>
-      <c r="E230" s="41"/>
-      <c r="F230" s="60"/>
+      <c r="E230" s="59"/>
+      <c r="F230" s="53"/>
     </row>
     <row r="231" spans="1:6" ht="13">
       <c r="A231" s="45"/>
@@ -3135,11 +3233,11 @@
       <c r="F231" s="49"/>
     </row>
     <row r="232" spans="1:6" ht="13">
-      <c r="A232" s="62"/>
-      <c r="B232" s="59"/>
-      <c r="C232" s="50"/>
-      <c r="D232" s="51"/>
-      <c r="E232" s="59"/>
+      <c r="A232" s="61"/>
+      <c r="B232" s="57"/>
+      <c r="C232" s="42"/>
+      <c r="D232" s="43"/>
+      <c r="E232" s="41"/>
       <c r="F232" s="53"/>
     </row>
     <row r="233" spans="1:6" ht="13">
@@ -3153,26 +3251,26 @@
     <row r="234" spans="1:6" ht="13">
       <c r="A234" s="61"/>
       <c r="B234" s="57"/>
-      <c r="C234" s="42"/>
-      <c r="D234" s="43"/>
-      <c r="E234" s="41"/>
+      <c r="C234" s="67"/>
+      <c r="D234" s="68"/>
+      <c r="E234" s="57"/>
       <c r="F234" s="53"/>
     </row>
     <row r="235" spans="1:6" ht="13">
-      <c r="A235" s="45"/>
-      <c r="B235" s="46"/>
-      <c r="C235" s="47"/>
-      <c r="D235" s="48"/>
-      <c r="E235" s="46"/>
+      <c r="A235" s="63"/>
+      <c r="B235" s="56"/>
+      <c r="C235" s="37"/>
+      <c r="D235" s="38"/>
+      <c r="E235" s="36"/>
       <c r="F235" s="49"/>
     </row>
     <row r="236" spans="1:6" ht="13">
-      <c r="A236" s="61"/>
-      <c r="B236" s="57"/>
-      <c r="C236" s="67"/>
-      <c r="D236" s="68"/>
-      <c r="E236" s="57"/>
-      <c r="F236" s="53"/>
+      <c r="A236" s="62"/>
+      <c r="B236" s="41"/>
+      <c r="C236" s="50"/>
+      <c r="D236" s="51"/>
+      <c r="E236" s="41"/>
+      <c r="F236" s="60"/>
     </row>
     <row r="237" spans="1:6" ht="13">
       <c r="A237" s="63"/>
@@ -3207,11 +3305,11 @@
       <c r="F240" s="60"/>
     </row>
     <row r="241" spans="1:6" ht="13">
-      <c r="A241" s="63"/>
-      <c r="B241" s="56"/>
-      <c r="C241" s="37"/>
-      <c r="D241" s="38"/>
-      <c r="E241" s="36"/>
+      <c r="A241" s="45"/>
+      <c r="B241" s="46"/>
+      <c r="C241" s="47"/>
+      <c r="D241" s="48"/>
+      <c r="E241" s="46"/>
       <c r="F241" s="49"/>
     </row>
     <row r="242" spans="1:6" ht="13">
@@ -3231,12 +3329,12 @@
       <c r="F243" s="49"/>
     </row>
     <row r="244" spans="1:6" ht="13">
-      <c r="A244" s="62"/>
-      <c r="B244" s="41"/>
-      <c r="C244" s="50"/>
-      <c r="D244" s="51"/>
+      <c r="A244" s="61"/>
+      <c r="B244" s="57"/>
+      <c r="C244" s="42"/>
+      <c r="D244" s="43"/>
       <c r="E244" s="41"/>
-      <c r="F244" s="60"/>
+      <c r="F244" s="53"/>
     </row>
     <row r="245" spans="1:6" ht="13">
       <c r="A245" s="45"/>
@@ -3249,34 +3347,34 @@
     <row r="246" spans="1:6" ht="13">
       <c r="A246" s="61"/>
       <c r="B246" s="57"/>
-      <c r="C246" s="42"/>
-      <c r="D246" s="43"/>
-      <c r="E246" s="41"/>
+      <c r="C246" s="67"/>
+      <c r="D246" s="68"/>
+      <c r="E246" s="57"/>
       <c r="F246" s="53"/>
     </row>
     <row r="247" spans="1:6" ht="13">
-      <c r="A247" s="45"/>
-      <c r="B247" s="46"/>
-      <c r="C247" s="47"/>
-      <c r="D247" s="48"/>
-      <c r="E247" s="46"/>
+      <c r="A247" s="63"/>
+      <c r="B247" s="56"/>
+      <c r="C247" s="37"/>
+      <c r="D247" s="38"/>
+      <c r="E247" s="36"/>
       <c r="F247" s="49"/>
     </row>
     <row r="248" spans="1:6" ht="13">
       <c r="A248" s="61"/>
       <c r="B248" s="57"/>
-      <c r="C248" s="67"/>
-      <c r="D248" s="68"/>
-      <c r="E248" s="57"/>
+      <c r="C248" s="42"/>
+      <c r="D248" s="43"/>
+      <c r="E248" s="41"/>
       <c r="F248" s="53"/>
     </row>
     <row r="249" spans="1:6" ht="13">
-      <c r="A249" s="63"/>
-      <c r="B249" s="56"/>
-      <c r="C249" s="37"/>
-      <c r="D249" s="38"/>
+      <c r="A249" s="45"/>
+      <c r="B249" s="36"/>
+      <c r="C249" s="47"/>
+      <c r="D249" s="48"/>
       <c r="E249" s="36"/>
-      <c r="F249" s="49"/>
+      <c r="F249" s="66"/>
     </row>
     <row r="250" spans="1:6" ht="13">
       <c r="A250" s="61"/>
@@ -3288,27 +3386,27 @@
     </row>
     <row r="251" spans="1:6" ht="13">
       <c r="A251" s="45"/>
-      <c r="B251" s="36"/>
+      <c r="B251" s="46"/>
       <c r="C251" s="47"/>
       <c r="D251" s="48"/>
-      <c r="E251" s="36"/>
-      <c r="F251" s="66"/>
+      <c r="E251" s="46"/>
+      <c r="F251" s="49"/>
     </row>
     <row r="252" spans="1:6" ht="13">
-      <c r="A252" s="61"/>
-      <c r="B252" s="57"/>
-      <c r="C252" s="42"/>
-      <c r="D252" s="43"/>
-      <c r="E252" s="41"/>
+      <c r="A252" s="62"/>
+      <c r="B252" s="59"/>
+      <c r="C252" s="50"/>
+      <c r="D252" s="51"/>
+      <c r="E252" s="59"/>
       <c r="F252" s="53"/>
     </row>
     <row r="253" spans="1:6" ht="13">
       <c r="A253" s="45"/>
-      <c r="B253" s="46"/>
+      <c r="B253" s="36"/>
       <c r="C253" s="47"/>
       <c r="D253" s="48"/>
-      <c r="E253" s="46"/>
-      <c r="F253" s="49"/>
+      <c r="E253" s="36"/>
+      <c r="F253" s="66"/>
     </row>
     <row r="254" spans="1:6" ht="13">
       <c r="A254" s="62"/>
@@ -3319,44 +3417,44 @@
       <c r="F254" s="53"/>
     </row>
     <row r="255" spans="1:6" ht="13">
-      <c r="A255" s="45"/>
-      <c r="B255" s="36"/>
-      <c r="C255" s="47"/>
-      <c r="D255" s="48"/>
+      <c r="A255" s="63"/>
+      <c r="B255" s="56"/>
+      <c r="C255" s="37"/>
+      <c r="D255" s="38"/>
       <c r="E255" s="36"/>
-      <c r="F255" s="66"/>
+      <c r="F255" s="49"/>
     </row>
     <row r="256" spans="1:6" ht="13">
-      <c r="A256" s="62"/>
-      <c r="B256" s="59"/>
-      <c r="C256" s="50"/>
-      <c r="D256" s="51"/>
-      <c r="E256" s="59"/>
+      <c r="A256" s="61"/>
+      <c r="B256" s="57"/>
+      <c r="C256" s="67"/>
+      <c r="D256" s="68"/>
+      <c r="E256" s="57"/>
       <c r="F256" s="53"/>
     </row>
     <row r="257" spans="1:6" ht="13">
-      <c r="A257" s="63"/>
-      <c r="B257" s="56"/>
-      <c r="C257" s="37"/>
-      <c r="D257" s="38"/>
+      <c r="A257" s="45"/>
+      <c r="B257" s="36"/>
+      <c r="C257" s="47"/>
+      <c r="D257" s="48"/>
       <c r="E257" s="36"/>
-      <c r="F257" s="49"/>
+      <c r="F257" s="66"/>
     </row>
     <row r="258" spans="1:6" ht="13">
       <c r="A258" s="61"/>
       <c r="B258" s="57"/>
-      <c r="C258" s="67"/>
-      <c r="D258" s="68"/>
-      <c r="E258" s="57"/>
+      <c r="C258" s="42"/>
+      <c r="D258" s="43"/>
+      <c r="E258" s="41"/>
       <c r="F258" s="53"/>
     </row>
     <row r="259" spans="1:6" ht="13">
       <c r="A259" s="45"/>
-      <c r="B259" s="36"/>
+      <c r="B259" s="46"/>
       <c r="C259" s="47"/>
       <c r="D259" s="48"/>
-      <c r="E259" s="36"/>
-      <c r="F259" s="66"/>
+      <c r="E259" s="46"/>
+      <c r="F259" s="49"/>
     </row>
     <row r="260" spans="1:6" ht="13">
       <c r="A260" s="61"/>
@@ -3368,11 +3466,11 @@
     </row>
     <row r="261" spans="1:6" ht="13">
       <c r="A261" s="45"/>
-      <c r="B261" s="46"/>
+      <c r="B261" s="36"/>
       <c r="C261" s="47"/>
       <c r="D261" s="48"/>
-      <c r="E261" s="46"/>
-      <c r="F261" s="49"/>
+      <c r="E261" s="36"/>
+      <c r="F261" s="66"/>
     </row>
     <row r="262" spans="1:6" ht="13">
       <c r="A262" s="61"/>
@@ -3391,28 +3489,28 @@
       <c r="F263" s="66"/>
     </row>
     <row r="264" spans="1:6" ht="13">
-      <c r="A264" s="61"/>
-      <c r="B264" s="57"/>
-      <c r="C264" s="42"/>
-      <c r="D264" s="43"/>
+      <c r="A264" s="62"/>
+      <c r="B264" s="41"/>
+      <c r="C264" s="50"/>
+      <c r="D264" s="51"/>
       <c r="E264" s="41"/>
-      <c r="F264" s="53"/>
+      <c r="F264" s="60"/>
     </row>
     <row r="265" spans="1:6" ht="13">
-      <c r="A265" s="45"/>
-      <c r="B265" s="36"/>
-      <c r="C265" s="47"/>
-      <c r="D265" s="48"/>
+      <c r="A265" s="63"/>
+      <c r="B265" s="56"/>
+      <c r="C265" s="37"/>
+      <c r="D265" s="38"/>
       <c r="E265" s="36"/>
-      <c r="F265" s="66"/>
+      <c r="F265" s="49"/>
     </row>
     <row r="266" spans="1:6" ht="13">
-      <c r="A266" s="62"/>
-      <c r="B266" s="41"/>
-      <c r="C266" s="50"/>
-      <c r="D266" s="51"/>
-      <c r="E266" s="41"/>
-      <c r="F266" s="60"/>
+      <c r="A266" s="61"/>
+      <c r="B266" s="57"/>
+      <c r="C266" s="67"/>
+      <c r="D266" s="68"/>
+      <c r="E266" s="57"/>
+      <c r="F266" s="53"/>
     </row>
     <row r="267" spans="1:6" ht="13">
       <c r="A267" s="63"/>
@@ -3425,9 +3523,9 @@
     <row r="268" spans="1:6" ht="13">
       <c r="A268" s="61"/>
       <c r="B268" s="57"/>
-      <c r="C268" s="67"/>
-      <c r="D268" s="68"/>
-      <c r="E268" s="57"/>
+      <c r="C268" s="42"/>
+      <c r="D268" s="43"/>
+      <c r="E268" s="41"/>
       <c r="F268" s="53"/>
     </row>
     <row r="269" spans="1:6" ht="13">
@@ -3439,19 +3537,19 @@
       <c r="F269" s="49"/>
     </row>
     <row r="270" spans="1:6" ht="13">
-      <c r="A270" s="61"/>
-      <c r="B270" s="57"/>
-      <c r="C270" s="42"/>
-      <c r="D270" s="43"/>
+      <c r="A270" s="62"/>
+      <c r="B270" s="41"/>
+      <c r="C270" s="50"/>
+      <c r="D270" s="51"/>
       <c r="E270" s="41"/>
-      <c r="F270" s="53"/>
+      <c r="F270" s="60"/>
     </row>
     <row r="271" spans="1:6" ht="13">
-      <c r="A271" s="63"/>
-      <c r="B271" s="56"/>
-      <c r="C271" s="37"/>
-      <c r="D271" s="38"/>
-      <c r="E271" s="36"/>
+      <c r="A271" s="45"/>
+      <c r="B271" s="46"/>
+      <c r="C271" s="47"/>
+      <c r="D271" s="48"/>
+      <c r="E271" s="46"/>
       <c r="F271" s="49"/>
     </row>
     <row r="272" spans="1:6" ht="13">
@@ -3472,27 +3570,27 @@
     </row>
     <row r="274" spans="1:6" ht="13">
       <c r="A274" s="62"/>
-      <c r="B274" s="41"/>
+      <c r="B274" s="59"/>
       <c r="C274" s="50"/>
       <c r="D274" s="51"/>
-      <c r="E274" s="41"/>
-      <c r="F274" s="60"/>
+      <c r="E274" s="59"/>
+      <c r="F274" s="53"/>
     </row>
     <row r="275" spans="1:6" ht="13">
-      <c r="A275" s="45"/>
-      <c r="B275" s="46"/>
-      <c r="C275" s="47"/>
-      <c r="D275" s="48"/>
-      <c r="E275" s="46"/>
-      <c r="F275" s="49"/>
+      <c r="A275" s="79"/>
+      <c r="B275" s="75"/>
+      <c r="C275" s="77"/>
+      <c r="D275" s="78"/>
+      <c r="E275" s="75"/>
+      <c r="F275" s="75"/>
     </row>
     <row r="276" spans="1:6" ht="13">
-      <c r="A276" s="62"/>
-      <c r="B276" s="59"/>
-      <c r="C276" s="50"/>
-      <c r="D276" s="51"/>
-      <c r="E276" s="59"/>
-      <c r="F276" s="53"/>
+      <c r="A276" s="79"/>
+      <c r="B276" s="75"/>
+      <c r="C276" s="77"/>
+      <c r="D276" s="78"/>
+      <c r="E276" s="75"/>
+      <c r="F276" s="75"/>
     </row>
     <row r="277" spans="1:6" ht="13">
       <c r="A277" s="79"/>
@@ -3855,7 +3953,7 @@
       <c r="F321" s="75"/>
     </row>
     <row r="322" spans="1:6" ht="13">
-      <c r="A322" s="79"/>
+      <c r="A322" s="75"/>
       <c r="B322" s="75"/>
       <c r="C322" s="77"/>
       <c r="D322" s="78"/>
@@ -3863,7 +3961,7 @@
       <c r="F322" s="75"/>
     </row>
     <row r="323" spans="1:6" ht="13">
-      <c r="A323" s="79"/>
+      <c r="A323" s="75"/>
       <c r="B323" s="75"/>
       <c r="C323" s="77"/>
       <c r="D323" s="78"/>
@@ -4455,20 +4553,16 @@
       <c r="F396" s="75"/>
     </row>
     <row r="397" spans="1:6" ht="13">
-      <c r="A397" s="75"/>
-      <c r="B397" s="75"/>
-      <c r="C397" s="77"/>
-      <c r="D397" s="78"/>
-      <c r="E397" s="75"/>
-      <c r="F397" s="75"/>
+      <c r="B397" s="85"/>
+      <c r="C397" s="76"/>
+      <c r="D397" s="80"/>
+      <c r="F397" s="81"/>
     </row>
     <row r="398" spans="1:6" ht="13">
-      <c r="A398" s="75"/>
-      <c r="B398" s="75"/>
-      <c r="C398" s="77"/>
-      <c r="D398" s="78"/>
-      <c r="E398" s="75"/>
-      <c r="F398" s="75"/>
+      <c r="B398" s="85"/>
+      <c r="C398" s="76"/>
+      <c r="D398" s="80"/>
+      <c r="F398" s="81"/>
     </row>
     <row r="399" spans="1:6" ht="13">
       <c r="B399" s="85"/>
@@ -4492,13 +4586,13 @@
       <c r="B402" s="85"/>
       <c r="C402" s="76"/>
       <c r="D402" s="80"/>
-      <c r="F402" s="81"/>
+      <c r="F402" s="82"/>
     </row>
     <row r="403" spans="2:6" ht="13">
       <c r="B403" s="85"/>
       <c r="C403" s="76"/>
       <c r="D403" s="80"/>
-      <c r="F403" s="81"/>
+      <c r="F403" s="82"/>
     </row>
     <row r="404" spans="2:6" ht="13">
       <c r="B404" s="85"/>
@@ -4927,7 +5021,7 @@
       <c r="F474" s="82"/>
     </row>
     <row r="475" spans="2:6" ht="13">
-      <c r="B475" s="85"/>
+      <c r="B475" s="86"/>
       <c r="C475" s="76"/>
       <c r="D475" s="80"/>
       <c r="F475" s="82"/>
@@ -4938,20 +5032,20 @@
       <c r="D476" s="80"/>
       <c r="F476" s="82"/>
     </row>
-    <row r="477" spans="2:6" ht="13">
-      <c r="B477" s="86"/>
-      <c r="C477" s="76"/>
+    <row r="477" spans="2:6" ht="14">
+      <c r="B477" s="85"/>
+      <c r="C477" s="83"/>
       <c r="D477" s="80"/>
       <c r="F477" s="82"/>
     </row>
-    <row r="478" spans="2:6" ht="13">
+    <row r="478" spans="2:6" ht="14">
       <c r="B478" s="85"/>
-      <c r="C478" s="76"/>
+      <c r="C478" s="83"/>
       <c r="D478" s="80"/>
       <c r="F478" s="82"/>
     </row>
     <row r="479" spans="2:6" ht="14">
-      <c r="B479" s="85"/>
+      <c r="B479" s="86"/>
       <c r="C479" s="83"/>
       <c r="D479" s="80"/>
       <c r="F479" s="82"/>
@@ -4963,15 +5057,16 @@
       <c r="F480" s="82"/>
     </row>
     <row r="481" spans="1:6" ht="14">
-      <c r="B481" s="86"/>
+      <c r="B481" s="85"/>
       <c r="C481" s="83"/>
       <c r="D481" s="80"/>
       <c r="F481" s="82"/>
     </row>
     <row r="482" spans="1:6" ht="14">
-      <c r="B482" s="85"/>
+      <c r="B482" s="87"/>
       <c r="C482" s="83"/>
       <c r="D482" s="80"/>
+      <c r="E482" s="84"/>
       <c r="F482" s="82"/>
     </row>
     <row r="483" spans="1:6" ht="14">
@@ -4981,10 +5076,9 @@
       <c r="F483" s="82"/>
     </row>
     <row r="484" spans="1:6" ht="14">
-      <c r="B484" s="87"/>
+      <c r="B484" s="85"/>
       <c r="C484" s="83"/>
       <c r="D484" s="80"/>
-      <c r="E484" s="84"/>
       <c r="F484" s="82"/>
     </row>
     <row r="485" spans="1:6" ht="14">
@@ -4994,13 +5088,13 @@
       <c r="F485" s="82"/>
     </row>
     <row r="486" spans="1:6" ht="14">
-      <c r="B486" s="85"/>
+      <c r="B486" s="87"/>
       <c r="C486" s="83"/>
       <c r="D486" s="80"/>
       <c r="F486" s="82"/>
     </row>
     <row r="487" spans="1:6" ht="14">
-      <c r="B487" s="85"/>
+      <c r="B487" s="87"/>
       <c r="C487" s="83"/>
       <c r="D487" s="80"/>
       <c r="F487" s="82"/>
@@ -5017,17 +5111,21 @@
       <c r="D489" s="80"/>
       <c r="F489" s="82"/>
     </row>
-    <row r="490" spans="1:6" ht="14">
-      <c r="B490" s="87"/>
-      <c r="C490" s="83"/>
-      <c r="D490" s="80"/>
-      <c r="F490" s="82"/>
-    </row>
-    <row r="491" spans="1:6" ht="14">
-      <c r="B491" s="87"/>
-      <c r="C491" s="83"/>
-      <c r="D491" s="80"/>
-      <c r="F491" s="82"/>
+    <row r="490" spans="1:6" ht="13">
+      <c r="A490" s="19"/>
+      <c r="B490" s="20"/>
+      <c r="C490" s="21"/>
+      <c r="D490" s="22"/>
+      <c r="E490" s="20"/>
+      <c r="F490" s="30"/>
+    </row>
+    <row r="491" spans="1:6" ht="13">
+      <c r="A491" s="14"/>
+      <c r="B491" s="15"/>
+      <c r="C491" s="16"/>
+      <c r="D491" s="17"/>
+      <c r="E491" s="15"/>
+      <c r="F491" s="69"/>
     </row>
     <row r="492" spans="1:6" ht="13">
       <c r="A492" s="19"/>
@@ -9094,39 +9192,23 @@
       <c r="F999" s="69"/>
     </row>
     <row r="1000" spans="1:6" ht="13">
-      <c r="A1000" s="19"/>
-      <c r="B1000" s="20"/>
-      <c r="C1000" s="21"/>
-      <c r="D1000" s="22"/>
-      <c r="E1000" s="20"/>
-      <c r="F1000" s="30"/>
-    </row>
-    <row r="1001" spans="1:6" ht="13">
-      <c r="A1001" s="14"/>
-      <c r="B1001" s="15"/>
-      <c r="C1001" s="16"/>
-      <c r="D1001" s="17"/>
-      <c r="E1001" s="15"/>
-      <c r="F1001" s="69"/>
-    </row>
-    <row r="1002" spans="1:6" ht="13">
-      <c r="A1002" s="70"/>
-      <c r="B1002" s="71"/>
-      <c r="C1002" s="72"/>
-      <c r="D1002" s="73"/>
-      <c r="E1002" s="71"/>
-      <c r="F1002" s="74"/>
+      <c r="A1000" s="70"/>
+      <c r="B1000" s="71"/>
+      <c r="C1000" s="72"/>
+      <c r="D1000" s="73"/>
+      <c r="E1000" s="71"/>
+      <c r="F1000" s="74"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D399:D1002 D24:D276" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>OR(TIMEVALUE(TEXT(D24, "hh:mm:ss"))=D24, AND(ISNUMBER(D24), LEFT(CELL("format", D24))="D"))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D397:D1000 D29:D274" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>OR(TIMEVALUE(TEXT(D29, "hh:mm:ss"))=D29, AND(ISNUMBER(D29), LEFT(CELL("format", D29))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="C399:C1002 C22 C24:C276" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>OR(NOT(ISERROR(DATEVALUE(C22))), AND(ISNUMBER(C22), LEFT(CELL("format", C22))="D"))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="C397:C1000 C10 C29:C274" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>OR(NOT(ISERROR(DATEVALUE(C10))), AND(ISNUMBER(C10), LEFT(CELL("format", C10))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F399:F1002 F14:F20 F24:F276" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>AND(ISNUMBER(F14),(NOT(OR(NOT(ISERROR(DATEVALUE(F14))), AND(ISNUMBER(F14), LEFT(CELL("format", F14))="D")))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F397:F1000 F2:F8 F29:F274" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>AND(ISNUMBER(F2),(NOT(OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
